--- a/UATtracking.xlsx
+++ b/UATtracking.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ259"/>
+  <dimension ref="A1:BC259"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -689,6 +689,21 @@
           <t>0108</t>
         </is>
       </c>
+      <c r="BA1" s="1" t="inlineStr">
+        <is>
+          <t>0109</t>
+        </is>
+      </c>
+      <c r="BB1" s="1" t="inlineStr">
+        <is>
+          <t>0110</t>
+        </is>
+      </c>
+      <c r="BC1" s="1" t="inlineStr">
+        <is>
+          <t>0113</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -945,6 +960,21 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BA2" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BB2" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BC2" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -1201,6 +1231,21 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BA3" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BB3" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BC3" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -1457,6 +1502,21 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BA4" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BB4" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BC4" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -1713,6 +1773,21 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BA5" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BB5" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BC5" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -1969,6 +2044,21 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BA6" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BB6" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BC6" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -2225,6 +2315,21 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BA7" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BB7" t="inlineStr">
+        <is>
+          <t>1error</t>
+        </is>
+      </c>
+      <c r="BC7" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -2481,6 +2586,21 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BA8" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BB8" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BC8" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -2737,6 +2857,21 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BA9" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BB9" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BC9" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -2993,6 +3128,21 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BA10" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BB10" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BC10" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -3249,6 +3399,21 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BA11" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BB11" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BC11" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -3505,6 +3670,21 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BA12" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BB12" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BC12" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -3761,6 +3941,21 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BA13" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BB13" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BC13" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -4017,6 +4212,21 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BA14" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BB14" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BC14" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -4273,6 +4483,21 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BA15" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BB15" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BC15" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -4529,6 +4754,21 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BA16" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BB16" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BC16" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -4785,6 +5025,21 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BA17" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BB17" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BC17" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -5041,6 +5296,21 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BA18" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BB18" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BC18" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -5297,6 +5567,21 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BA19" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BB19" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BC19" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -5553,6 +5838,21 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BA20" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BB20" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BC20" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -5809,6 +6109,21 @@
           <t>1error</t>
         </is>
       </c>
+      <c r="BA21" t="inlineStr">
+        <is>
+          <t>1error</t>
+        </is>
+      </c>
+      <c r="BB21" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BC21" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -6065,6 +6380,21 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BA22" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BB22" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BC22" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -6321,6 +6651,21 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BA23" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BB23" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BC23" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -6577,6 +6922,21 @@
           <t>1error</t>
         </is>
       </c>
+      <c r="BA24" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BB24" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BC24" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -6833,6 +7193,21 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BA25" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BB25" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BC25" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -7089,6 +7464,21 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BA26" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BB26" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BC26" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -7345,6 +7735,21 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BA27" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BB27" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BC27" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -7601,6 +8006,21 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BA28" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BB28" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BC28" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -7857,6 +8277,21 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BA29" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BB29" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BC29" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -8113,6 +8548,21 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BA30" t="inlineStr">
+        <is>
+          <t>2error</t>
+        </is>
+      </c>
+      <c r="BB30" t="inlineStr">
+        <is>
+          <t>2error</t>
+        </is>
+      </c>
+      <c r="BC30" t="inlineStr">
+        <is>
+          <t>2error</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -8369,6 +8819,21 @@
           <t>1error</t>
         </is>
       </c>
+      <c r="BA31" t="inlineStr">
+        <is>
+          <t>1error</t>
+        </is>
+      </c>
+      <c r="BB31" t="inlineStr">
+        <is>
+          <t>1error</t>
+        </is>
+      </c>
+      <c r="BC31" t="inlineStr">
+        <is>
+          <t>1error</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -8625,6 +9090,21 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BA32" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BB32" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BC32" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -8881,6 +9361,21 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BA33" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BB33" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BC33" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -9137,6 +9632,21 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BA34" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BB34" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BC34" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -9391,6 +9901,21 @@
           <t>offline</t>
         </is>
       </c>
+      <c r="BA35" t="inlineStr">
+        <is>
+          <t>offline</t>
+        </is>
+      </c>
+      <c r="BB35" t="inlineStr">
+        <is>
+          <t>offline</t>
+        </is>
+      </c>
+      <c r="BC35" t="inlineStr">
+        <is>
+          <t>offline</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -9647,6 +10172,21 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BA36" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BB36" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BC36" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -9903,6 +10443,21 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BA37" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BB37" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BC37" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -10159,6 +10714,21 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BA38" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BB38" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BC38" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -10415,6 +10985,21 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BA39" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BB39" t="inlineStr">
+        <is>
+          <t>1error</t>
+        </is>
+      </c>
+      <c r="BC39" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -10671,6 +11256,21 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BA40" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BB40" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BC40" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -10927,6 +11527,21 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BA41" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BB41" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BC41" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -11183,6 +11798,21 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BA42" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BB42" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BC42" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -11439,6 +12069,21 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BA43" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BB43" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BC43" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -11695,6 +12340,21 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BA44" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BB44" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BC44" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -11951,6 +12611,21 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BA45" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BB45" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BC45" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -12207,6 +12882,21 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BA46" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BB46" t="inlineStr">
+        <is>
+          <t>1error</t>
+        </is>
+      </c>
+      <c r="BC46" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -12463,6 +13153,21 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BA47" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BB47" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BC47" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -12719,6 +13424,21 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BA48" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BB48" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BC48" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -12975,6 +13695,21 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BA49" t="inlineStr">
+        <is>
+          <t>2error</t>
+        </is>
+      </c>
+      <c r="BB49" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BC49" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -13231,6 +13966,21 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BA50" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BB50" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BC50" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -13487,6 +14237,21 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BA51" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BB51" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BC51" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -13743,6 +14508,21 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BA52" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BB52" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BC52" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -13997,6 +14777,21 @@
           <t>offline</t>
         </is>
       </c>
+      <c r="BA53" t="inlineStr">
+        <is>
+          <t>offline</t>
+        </is>
+      </c>
+      <c r="BB53" t="inlineStr">
+        <is>
+          <t>offline</t>
+        </is>
+      </c>
+      <c r="BC53" t="inlineStr">
+        <is>
+          <t>offline</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -14251,6 +15046,21 @@
           <t>offline</t>
         </is>
       </c>
+      <c r="BA54" t="inlineStr">
+        <is>
+          <t>offline</t>
+        </is>
+      </c>
+      <c r="BB54" t="inlineStr">
+        <is>
+          <t>offline</t>
+        </is>
+      </c>
+      <c r="BC54" t="inlineStr">
+        <is>
+          <t>offline</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -14507,6 +15317,21 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BA55" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BB55" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BC55" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -14763,6 +15588,21 @@
           <t>1error</t>
         </is>
       </c>
+      <c r="BA56" t="inlineStr">
+        <is>
+          <t>1error</t>
+        </is>
+      </c>
+      <c r="BB56" t="inlineStr">
+        <is>
+          <t>1error</t>
+        </is>
+      </c>
+      <c r="BC56" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -15019,6 +15859,21 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BA57" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BB57" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BC57" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -15275,6 +16130,21 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BA58" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BB58" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BC58" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -15531,6 +16401,21 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BA59" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BB59" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BC59" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -15787,6 +16672,21 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BA60" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BB60" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BC60" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -16043,6 +16943,21 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BA61" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BB61" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BC61" t="inlineStr">
+        <is>
+          <t>1error</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -16299,6 +17214,21 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BA62" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BB62" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BC62" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -16555,6 +17485,21 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BA63" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BB63" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BC63" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -16811,6 +17756,21 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BA64" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BB64" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BC64" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -17067,6 +18027,21 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BA65" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BB65" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BC65" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -17323,6 +18298,21 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BA66" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BB66" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BC66" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -17579,6 +18569,21 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BA67" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BB67" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BC67" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -17835,6 +18840,21 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BA68" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BB68" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BC68" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -18091,6 +19111,21 @@
           <t>2error</t>
         </is>
       </c>
+      <c r="BA69" t="inlineStr">
+        <is>
+          <t>2error</t>
+        </is>
+      </c>
+      <c r="BB69" t="inlineStr">
+        <is>
+          <t>2error</t>
+        </is>
+      </c>
+      <c r="BC69" t="inlineStr">
+        <is>
+          <t>2error</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -18347,6 +19382,21 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BA70" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BB70" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BC70" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -18603,6 +19653,21 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BA71" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BB71" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BC71" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -18859,6 +19924,21 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BA72" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BB72" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BC72" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -19115,6 +20195,21 @@
           <t>1error</t>
         </is>
       </c>
+      <c r="BA73" t="inlineStr">
+        <is>
+          <t>1error</t>
+        </is>
+      </c>
+      <c r="BB73" t="inlineStr">
+        <is>
+          <t>1error</t>
+        </is>
+      </c>
+      <c r="BC73" t="inlineStr">
+        <is>
+          <t>2error</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -19371,6 +20466,21 @@
           <t>1error</t>
         </is>
       </c>
+      <c r="BA74" t="inlineStr">
+        <is>
+          <t>1error</t>
+        </is>
+      </c>
+      <c r="BB74" t="inlineStr">
+        <is>
+          <t>1error</t>
+        </is>
+      </c>
+      <c r="BC74" t="inlineStr">
+        <is>
+          <t>1error</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -19627,6 +20737,21 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BA75" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BB75" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BC75" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -19883,6 +21008,21 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BA76" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BB76" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BC76" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
@@ -20139,6 +21279,21 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BA77" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BB77" t="inlineStr">
+        <is>
+          <t>1error</t>
+        </is>
+      </c>
+      <c r="BC77" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
@@ -20395,6 +21550,21 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BA78" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BB78" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BC78" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
@@ -20408,7 +21578,7 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
@@ -20649,6 +21819,21 @@
       <c r="AZ79" t="inlineStr">
         <is>
           <t>1error</t>
+        </is>
+      </c>
+      <c r="BA79" t="inlineStr">
+        <is>
+          <t>1error</t>
+        </is>
+      </c>
+      <c r="BB79" t="inlineStr">
+        <is>
+          <t>1error</t>
+        </is>
+      </c>
+      <c r="BC79" t="inlineStr">
+        <is>
+          <t>online</t>
         </is>
       </c>
     </row>
@@ -20905,6 +22090,21 @@
           <t>offline</t>
         </is>
       </c>
+      <c r="BA80" t="inlineStr">
+        <is>
+          <t>offline</t>
+        </is>
+      </c>
+      <c r="BB80" t="inlineStr">
+        <is>
+          <t>offline</t>
+        </is>
+      </c>
+      <c r="BC80" t="inlineStr">
+        <is>
+          <t>offline</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
@@ -21161,6 +22361,21 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BA81" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BB81" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BC81" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
@@ -21417,6 +22632,21 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BA82" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BB82" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BC82" t="inlineStr">
+        <is>
+          <t>1error</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
@@ -21673,6 +22903,21 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BA83" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BB83" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BC83" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
@@ -21929,6 +23174,21 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BA84" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BB84" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BC84" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
@@ -22185,6 +23445,21 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BA85" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BB85" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BC85" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
@@ -22441,6 +23716,21 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BA86" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BB86" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BC86" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
@@ -22697,6 +23987,21 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BA87" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BB87" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BC87" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
@@ -22953,6 +24258,21 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BA88" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BB88" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BC88" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
@@ -23209,6 +24529,21 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BA89" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BB89" t="inlineStr">
+        <is>
+          <t>2error</t>
+        </is>
+      </c>
+      <c r="BC89" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
@@ -23465,6 +24800,21 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BA90" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BB90" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BC90" t="inlineStr">
+        <is>
+          <t>2error</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
@@ -23721,6 +25071,21 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BA91" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BB91" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BC91" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
@@ -23977,6 +25342,21 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BA92" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BB92" t="inlineStr">
+        <is>
+          <t>1error</t>
+        </is>
+      </c>
+      <c r="BC92" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
@@ -24233,6 +25613,21 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BA93" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BB93" t="inlineStr">
+        <is>
+          <t>1error</t>
+        </is>
+      </c>
+      <c r="BC93" t="inlineStr">
+        <is>
+          <t>1error</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
@@ -24489,6 +25884,21 @@
           <t>1error</t>
         </is>
       </c>
+      <c r="BA94" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BB94" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BC94" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
@@ -24745,6 +26155,21 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BA95" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BB95" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BC95" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
@@ -25001,6 +26426,21 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BA96" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BB96" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BC96" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
@@ -25257,6 +26697,21 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BA97" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BB97" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BC97" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
@@ -25513,6 +26968,21 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BA98" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BB98" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BC98" t="inlineStr">
+        <is>
+          <t>2error</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
@@ -25769,6 +27239,21 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BA99" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BB99" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BC99" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
@@ -26025,6 +27510,21 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BA100" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BB100" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BC100" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
@@ -26281,6 +27781,21 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BA101" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BB101" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BC101" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
@@ -26537,6 +28052,21 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BA102" t="inlineStr">
+        <is>
+          <t>1error</t>
+        </is>
+      </c>
+      <c r="BB102" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BC102" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
@@ -26793,6 +28323,21 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BA103" t="inlineStr">
+        <is>
+          <t>1error</t>
+        </is>
+      </c>
+      <c r="BB103" t="inlineStr">
+        <is>
+          <t>1error</t>
+        </is>
+      </c>
+      <c r="BC103" t="inlineStr">
+        <is>
+          <t>1error</t>
+        </is>
+      </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
@@ -27049,6 +28594,21 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BA104" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BB104" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BC104" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
@@ -27305,6 +28865,21 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BA105" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BB105" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BC105" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
@@ -27318,7 +28893,7 @@
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
@@ -27557,6 +29132,21 @@
         </is>
       </c>
       <c r="AZ106" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BA106" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BB106" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BC106" t="inlineStr">
         <is>
           <t>online</t>
         </is>
@@ -27817,6 +29407,21 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BA107" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BB107" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BC107" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
@@ -28073,6 +29678,21 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BA108" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BB108" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BC108" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
@@ -28329,6 +29949,21 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BA109" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BB109" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BC109" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
@@ -28585,6 +30220,21 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BA110" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BB110" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BC110" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
@@ -28841,6 +30491,21 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BA111" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BB111" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BC111" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
@@ -29097,6 +30762,21 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BA112" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BB112" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BC112" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
@@ -29353,6 +31033,21 @@
           <t>1error</t>
         </is>
       </c>
+      <c r="BA113" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BB113" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BC113" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
@@ -29609,6 +31304,21 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BA114" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BB114" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BC114" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
@@ -29865,6 +31575,21 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BA115" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BB115" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BC115" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
@@ -30121,6 +31846,21 @@
           <t>1error</t>
         </is>
       </c>
+      <c r="BA116" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BB116" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BC116" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
@@ -30377,6 +32117,21 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BA117" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BB117" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BC117" t="inlineStr">
+        <is>
+          <t>1error</t>
+        </is>
+      </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
@@ -30633,6 +32388,21 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BA118" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BB118" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BC118" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
@@ -30887,6 +32657,21 @@
           <t>offline</t>
         </is>
       </c>
+      <c r="BA119" t="inlineStr">
+        <is>
+          <t>offline</t>
+        </is>
+      </c>
+      <c r="BB119" t="inlineStr">
+        <is>
+          <t>offline</t>
+        </is>
+      </c>
+      <c r="BC119" t="inlineStr">
+        <is>
+          <t>offline</t>
+        </is>
+      </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
@@ -31143,6 +32928,21 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BA120" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BB120" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BC120" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
@@ -31399,6 +33199,21 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BA121" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BB121" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BC121" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
@@ -31655,6 +33470,21 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BA122" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BB122" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BC122" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
@@ -31911,6 +33741,21 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BA123" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BB123" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BC123" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
@@ -32167,6 +34012,21 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BA124" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BB124" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BC124" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
@@ -32423,6 +34283,21 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BA125" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BB125" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BC125" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
@@ -32677,6 +34552,21 @@
           <t>offline</t>
         </is>
       </c>
+      <c r="BA126" t="inlineStr">
+        <is>
+          <t>offline</t>
+        </is>
+      </c>
+      <c r="BB126" t="inlineStr">
+        <is>
+          <t>offline</t>
+        </is>
+      </c>
+      <c r="BC126" t="inlineStr">
+        <is>
+          <t>offline</t>
+        </is>
+      </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
@@ -32933,6 +34823,21 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BA127" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BB127" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BC127" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
@@ -33189,6 +35094,21 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BA128" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BB128" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BC128" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
@@ -33445,6 +35365,21 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BA129" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BB129" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BC129" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
@@ -33701,6 +35636,21 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BA130" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BB130" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BC130" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
@@ -33957,6 +35907,21 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BA131" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BB131" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BC131" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
@@ -34213,6 +36178,21 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BA132" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BB132" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BC132" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
@@ -34467,6 +36447,21 @@
           <t>offline</t>
         </is>
       </c>
+      <c r="BA133" t="inlineStr">
+        <is>
+          <t>offline</t>
+        </is>
+      </c>
+      <c r="BB133" t="inlineStr">
+        <is>
+          <t>offline</t>
+        </is>
+      </c>
+      <c r="BC133" t="inlineStr">
+        <is>
+          <t>offline</t>
+        </is>
+      </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
@@ -34723,6 +36718,21 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BA134" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BB134" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BC134" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
@@ -34979,6 +36989,21 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BA135" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BB135" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BC135" t="inlineStr">
+        <is>
+          <t>1error</t>
+        </is>
+      </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
@@ -34992,7 +37017,7 @@
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E136" t="inlineStr">
@@ -35231,6 +37256,21 @@
         </is>
       </c>
       <c r="AZ136" t="inlineStr">
+        <is>
+          <t>1error</t>
+        </is>
+      </c>
+      <c r="BA136" t="inlineStr">
+        <is>
+          <t>1error</t>
+        </is>
+      </c>
+      <c r="BB136" t="inlineStr">
+        <is>
+          <t>2error</t>
+        </is>
+      </c>
+      <c r="BC136" t="inlineStr">
         <is>
           <t>1error</t>
         </is>
@@ -35491,6 +37531,21 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BA137" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BB137" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BC137" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
@@ -35745,6 +37800,21 @@
           <t>offline</t>
         </is>
       </c>
+      <c r="BA138" t="inlineStr">
+        <is>
+          <t>offline</t>
+        </is>
+      </c>
+      <c r="BB138" t="inlineStr">
+        <is>
+          <t>offline</t>
+        </is>
+      </c>
+      <c r="BC138" t="inlineStr">
+        <is>
+          <t>offline</t>
+        </is>
+      </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
@@ -36001,6 +38071,21 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BA139" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BB139" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BC139" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
@@ -36257,6 +38342,21 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BA140" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BB140" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BC140" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
@@ -36513,6 +38613,21 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BA141" t="inlineStr">
+        <is>
+          <t>1error</t>
+        </is>
+      </c>
+      <c r="BB141" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BC141" t="inlineStr">
+        <is>
+          <t>1error</t>
+        </is>
+      </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
@@ -36769,6 +38884,21 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BA142" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BB142" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BC142" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
@@ -37025,6 +39155,21 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BA143" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BB143" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BC143" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
@@ -37281,6 +39426,21 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BA144" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BB144" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BC144" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
@@ -37537,6 +39697,21 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BA145" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BB145" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BC145" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
@@ -37793,6 +39968,21 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BA146" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BB146" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BC146" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
@@ -38049,6 +40239,21 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BA147" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BB147" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BC147" t="inlineStr">
+        <is>
+          <t>2error</t>
+        </is>
+      </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
@@ -38305,6 +40510,21 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BA148" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BB148" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BC148" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
@@ -38561,6 +40781,21 @@
           <t>1error</t>
         </is>
       </c>
+      <c r="BA149" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BB149" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BC149" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
@@ -38817,6 +41052,21 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BA150" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BB150" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BC150" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
@@ -39073,6 +41323,21 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BA151" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BB151" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BC151" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
@@ -39327,6 +41592,21 @@
           <t>offline</t>
         </is>
       </c>
+      <c r="BA152" t="inlineStr">
+        <is>
+          <t>offline</t>
+        </is>
+      </c>
+      <c r="BB152" t="inlineStr">
+        <is>
+          <t>offline</t>
+        </is>
+      </c>
+      <c r="BC152" t="inlineStr">
+        <is>
+          <t>offline</t>
+        </is>
+      </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
@@ -39583,6 +41863,21 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BA153" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BB153" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BC153" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
@@ -39839,6 +42134,21 @@
           <t>1error</t>
         </is>
       </c>
+      <c r="BA154" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BB154" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BC154" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
@@ -40095,6 +42405,21 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BA155" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BB155" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BC155" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
@@ -40351,6 +42676,21 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BA156" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BB156" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BC156" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
@@ -40607,6 +42947,21 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BA157" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BB157" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BC157" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
@@ -40863,6 +43218,21 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BA158" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BB158" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BC158" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
@@ -40874,8 +43244,10 @@
       <c r="C159" t="n">
         <v>2</v>
       </c>
-      <c r="D159" t="n">
-        <v>2</v>
+      <c r="D159" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
       </c>
       <c r="E159" t="inlineStr">
         <is>
@@ -41115,6 +43487,21 @@
       <c r="AZ159" t="inlineStr">
         <is>
           <t>offline</t>
+        </is>
+      </c>
+      <c r="BA159" t="inlineStr">
+        <is>
+          <t>offline</t>
+        </is>
+      </c>
+      <c r="BB159" t="inlineStr">
+        <is>
+          <t>offline</t>
+        </is>
+      </c>
+      <c r="BC159" t="inlineStr">
+        <is>
+          <t>online</t>
         </is>
       </c>
     </row>
@@ -41373,6 +43760,21 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BA160" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BB160" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BC160" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
@@ -41629,6 +44031,21 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BA161" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BB161" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BC161" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
@@ -41885,6 +44302,21 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BA162" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BB162" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BC162" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
@@ -42141,6 +44573,21 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BA163" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BB163" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BC163" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
@@ -42397,6 +44844,21 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BA164" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BB164" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BC164" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
@@ -42653,6 +45115,21 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BA165" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BB165" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BC165" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
@@ -42909,6 +45386,21 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BA166" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BB166" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BC166" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
@@ -43165,6 +45657,21 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BA167" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BB167" t="inlineStr">
+        <is>
+          <t>1error</t>
+        </is>
+      </c>
+      <c r="BC167" t="inlineStr">
+        <is>
+          <t>1error</t>
+        </is>
+      </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
@@ -43421,6 +45928,21 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BA168" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BB168" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BC168" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
@@ -43677,6 +46199,21 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BA169" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BB169" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BC169" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
@@ -43933,6 +46470,21 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BA170" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BB170" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BC170" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
@@ -44189,6 +46741,21 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BA171" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BB171" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BC171" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
@@ -44445,6 +47012,21 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BA172" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BB172" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BC172" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
@@ -44701,6 +47283,21 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BA173" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BB173" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BC173" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
@@ -44957,6 +47554,21 @@
           <t>1error</t>
         </is>
       </c>
+      <c r="BA174" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BB174" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BC174" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
@@ -45213,6 +47825,21 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BA175" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BB175" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BC175" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
@@ -45469,6 +48096,21 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BA176" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BB176" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BC176" t="inlineStr">
+        <is>
+          <t>1error</t>
+        </is>
+      </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
@@ -45723,6 +48365,21 @@
           <t>offline</t>
         </is>
       </c>
+      <c r="BA177" t="inlineStr">
+        <is>
+          <t>offline</t>
+        </is>
+      </c>
+      <c r="BB177" t="inlineStr">
+        <is>
+          <t>offline</t>
+        </is>
+      </c>
+      <c r="BC177" t="inlineStr">
+        <is>
+          <t>offline</t>
+        </is>
+      </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
@@ -45979,6 +48636,21 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BA178" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BB178" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BC178" t="inlineStr">
+        <is>
+          <t>1error</t>
+        </is>
+      </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
@@ -46235,6 +48907,21 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BA179" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BB179" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BC179" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
@@ -46246,8 +48933,10 @@
       <c r="C180" t="n">
         <v>2</v>
       </c>
-      <c r="D180" t="n">
-        <v>2</v>
+      <c r="D180" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
       </c>
       <c r="E180" t="inlineStr">
         <is>
@@ -46487,6 +49176,21 @@
       <c r="AZ180" t="inlineStr">
         <is>
           <t>offline</t>
+        </is>
+      </c>
+      <c r="BA180" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BB180" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BC180" t="inlineStr">
+        <is>
+          <t>online</t>
         </is>
       </c>
     </row>
@@ -46745,6 +49449,21 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BA181" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BB181" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BC181" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
@@ -46999,6 +49718,21 @@
           <t>offline</t>
         </is>
       </c>
+      <c r="BA182" t="inlineStr">
+        <is>
+          <t>offline</t>
+        </is>
+      </c>
+      <c r="BB182" t="inlineStr">
+        <is>
+          <t>offline</t>
+        </is>
+      </c>
+      <c r="BC182" t="inlineStr">
+        <is>
+          <t>offline</t>
+        </is>
+      </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
@@ -47253,6 +49987,21 @@
           <t>offline</t>
         </is>
       </c>
+      <c r="BA183" t="inlineStr">
+        <is>
+          <t>offline</t>
+        </is>
+      </c>
+      <c r="BB183" t="inlineStr">
+        <is>
+          <t>offline</t>
+        </is>
+      </c>
+      <c r="BC183" t="inlineStr">
+        <is>
+          <t>offline</t>
+        </is>
+      </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
@@ -47509,6 +50258,21 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BA184" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BB184" t="inlineStr">
+        <is>
+          <t>1error</t>
+        </is>
+      </c>
+      <c r="BC184" t="inlineStr">
+        <is>
+          <t>1error</t>
+        </is>
+      </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
@@ -47765,6 +50529,21 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BA185" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BB185" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BC185" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
@@ -48021,6 +50800,21 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BA186" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BB186" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BC186" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
@@ -48277,6 +51071,21 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BA187" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BB187" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BC187" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
@@ -48533,6 +51342,21 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BA188" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BB188" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BC188" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
@@ -48789,6 +51613,21 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BA189" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BB189" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BC189" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
@@ -49045,6 +51884,21 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BA190" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BB190" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BC190" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
@@ -49301,6 +52155,21 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BA191" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BB191" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BC191" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
@@ -49557,6 +52426,21 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BA192" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BB192" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BC192" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
@@ -49813,6 +52697,21 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BA193" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BB193" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BC193" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
@@ -50069,6 +52968,21 @@
           <t>1error</t>
         </is>
       </c>
+      <c r="BA194" t="inlineStr">
+        <is>
+          <t>1error</t>
+        </is>
+      </c>
+      <c r="BB194" t="inlineStr">
+        <is>
+          <t>1error</t>
+        </is>
+      </c>
+      <c r="BC194" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
@@ -50325,6 +53239,21 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BA195" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BB195" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BC195" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
@@ -50581,6 +53510,21 @@
           <t>1error</t>
         </is>
       </c>
+      <c r="BA196" t="inlineStr">
+        <is>
+          <t>1error</t>
+        </is>
+      </c>
+      <c r="BB196" t="inlineStr">
+        <is>
+          <t>1error</t>
+        </is>
+      </c>
+      <c r="BC196" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
@@ -50837,6 +53781,21 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BA197" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BB197" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BC197" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
@@ -51093,6 +54052,21 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BA198" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BB198" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BC198" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
@@ -51349,6 +54323,21 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BA199" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BB199" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BC199" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
@@ -51605,6 +54594,21 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BA200" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BB200" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BC200" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
@@ -51861,6 +54865,21 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BA201" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BB201" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BC201" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
@@ -52117,6 +55136,21 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BA202" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BB202" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BC202" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
@@ -52373,6 +55407,21 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BA203" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BB203" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BC203" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
@@ -52629,6 +55678,21 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BA204" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BB204" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BC204" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
@@ -52885,6 +55949,21 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BA205" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BB205" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BC205" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
@@ -53141,6 +56220,21 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BA206" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BB206" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BC206" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
@@ -53397,6 +56491,21 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BA207" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BB207" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BC207" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
@@ -53653,6 +56762,21 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BA208" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BB208" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BC208" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
@@ -53909,6 +57033,21 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BA209" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BB209" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BC209" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
@@ -54165,6 +57304,21 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BA210" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BB210" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BC210" t="inlineStr">
+        <is>
+          <t>1error</t>
+        </is>
+      </c>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
@@ -54421,6 +57575,21 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BA211" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BB211" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BC211" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
@@ -54677,6 +57846,21 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BA212" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BB212" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BC212" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
@@ -54933,6 +58117,21 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BA213" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BB213" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BC213" t="inlineStr">
+        <is>
+          <t>1error</t>
+        </is>
+      </c>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
@@ -55189,6 +58388,21 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BA214" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BB214" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BC214" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
@@ -55445,6 +58659,21 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BA215" t="inlineStr">
+        <is>
+          <t>1error</t>
+        </is>
+      </c>
+      <c r="BB215" t="inlineStr">
+        <is>
+          <t>1error</t>
+        </is>
+      </c>
+      <c r="BC215" t="inlineStr">
+        <is>
+          <t>1error</t>
+        </is>
+      </c>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
@@ -55701,6 +58930,21 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BA216" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BB216" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BC216" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
@@ -55957,6 +59201,21 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BA217" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BB217" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BC217" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
@@ -56213,6 +59472,21 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BA218" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BB218" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BC218" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
@@ -56469,6 +59743,21 @@
           <t>1error</t>
         </is>
       </c>
+      <c r="BA219" t="inlineStr">
+        <is>
+          <t>1error</t>
+        </is>
+      </c>
+      <c r="BB219" t="inlineStr">
+        <is>
+          <t>1error</t>
+        </is>
+      </c>
+      <c r="BC219" t="inlineStr">
+        <is>
+          <t>1error</t>
+        </is>
+      </c>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
@@ -56725,6 +60014,21 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BA220" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BB220" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BC220" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="221">
       <c r="A221" t="inlineStr">
@@ -56981,6 +60285,21 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BA221" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BB221" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BC221" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="222">
       <c r="A222" t="inlineStr">
@@ -57237,6 +60556,21 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BA222" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BB222" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BC222" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr">
@@ -57493,6 +60827,21 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BA223" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BB223" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BC223" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="224">
       <c r="A224" t="inlineStr">
@@ -57749,6 +61098,21 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BA224" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BB224" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BC224" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="225">
       <c r="A225" t="inlineStr">
@@ -58005,6 +61369,21 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BA225" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BB225" t="inlineStr">
+        <is>
+          <t>1error</t>
+        </is>
+      </c>
+      <c r="BC225" t="inlineStr">
+        <is>
+          <t>1error</t>
+        </is>
+      </c>
     </row>
     <row r="226">
       <c r="A226" t="inlineStr">
@@ -58261,6 +61640,21 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BA226" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BB226" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BC226" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="227">
       <c r="A227" t="inlineStr">
@@ -58517,6 +61911,21 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BA227" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BB227" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BC227" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="228">
       <c r="A228" t="inlineStr">
@@ -58773,6 +62182,21 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BA228" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BB228" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BC228" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="229">
       <c r="A229" t="inlineStr">
@@ -59029,6 +62453,21 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BA229" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BB229" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BC229" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="230">
       <c r="A230" t="inlineStr">
@@ -59285,6 +62724,21 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BA230" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BB230" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BC230" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="231">
       <c r="A231" t="inlineStr">
@@ -59541,6 +62995,21 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BA231" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BB231" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BC231" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="232">
       <c r="A232" t="inlineStr">
@@ -59797,6 +63266,21 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BA232" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BB232" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BC232" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="233">
       <c r="A233" t="inlineStr">
@@ -60053,6 +63537,21 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BA233" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BB233" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BC233" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="234">
       <c r="A234" t="inlineStr">
@@ -60309,6 +63808,21 @@
           <t>1error</t>
         </is>
       </c>
+      <c r="BA234" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BB234" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BC234" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="235">
       <c r="A235" t="inlineStr">
@@ -60565,6 +64079,21 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BA235" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BB235" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BC235" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="236">
       <c r="A236" t="inlineStr">
@@ -60821,6 +64350,21 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BA236" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BB236" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BC236" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="237">
       <c r="A237" t="inlineStr">
@@ -61077,6 +64621,21 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BA237" t="inlineStr">
+        <is>
+          <t>1error</t>
+        </is>
+      </c>
+      <c r="BB237" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BC237" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="238">
       <c r="A238" t="inlineStr">
@@ -61333,6 +64892,21 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BA238" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BB238" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BC238" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="239">
       <c r="A239" t="inlineStr">
@@ -61589,6 +65163,21 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BA239" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BB239" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BC239" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="240">
       <c r="A240" t="inlineStr">
@@ -61845,6 +65434,21 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BA240" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BB240" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BC240" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="241">
       <c r="A241" t="inlineStr">
@@ -62101,6 +65705,21 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BA241" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BB241" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BC241" t="inlineStr">
+        <is>
+          <t>1error</t>
+        </is>
+      </c>
     </row>
     <row r="242">
       <c r="A242" t="inlineStr">
@@ -62357,6 +65976,21 @@
           <t>1error</t>
         </is>
       </c>
+      <c r="BA242" t="inlineStr">
+        <is>
+          <t>1error</t>
+        </is>
+      </c>
+      <c r="BB242" t="inlineStr">
+        <is>
+          <t>1error</t>
+        </is>
+      </c>
+      <c r="BC242" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="243">
       <c r="A243" t="inlineStr">
@@ -62613,6 +66247,21 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BA243" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BB243" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BC243" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="244">
       <c r="A244" t="inlineStr">
@@ -62865,6 +66514,21 @@
         </is>
       </c>
       <c r="AZ244" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BA244" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BB244" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BC244" t="inlineStr">
         <is>
           <t>online</t>
         </is>
@@ -63089,6 +66753,21 @@
         </is>
       </c>
       <c r="AZ245" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BA245" t="inlineStr">
+        <is>
+          <t>1error</t>
+        </is>
+      </c>
+      <c r="BB245" t="inlineStr">
+        <is>
+          <t>1error</t>
+        </is>
+      </c>
+      <c r="BC245" t="inlineStr">
         <is>
           <t>online</t>
         </is>
@@ -63285,6 +66964,21 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BA246" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BB246" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BC246" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="247">
       <c r="A247" t="inlineStr">
@@ -63473,6 +67167,21 @@
         </is>
       </c>
       <c r="AZ247" t="inlineStr">
+        <is>
+          <t>1error</t>
+        </is>
+      </c>
+      <c r="BA247" t="inlineStr">
+        <is>
+          <t>1error</t>
+        </is>
+      </c>
+      <c r="BB247" t="inlineStr">
+        <is>
+          <t>1error</t>
+        </is>
+      </c>
+      <c r="BC247" t="inlineStr">
         <is>
           <t>1error</t>
         </is>
@@ -63637,6 +67346,21 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BA248" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BB248" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BC248" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="249">
       <c r="A249" t="inlineStr">
@@ -63793,6 +67517,21 @@
         </is>
       </c>
       <c r="AZ249" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BA249" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BB249" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BC249" t="inlineStr">
         <is>
           <t>online</t>
         </is>
@@ -63953,6 +67692,21 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BA250" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BB250" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BC250" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="251">
       <c r="A251" t="inlineStr">
@@ -64109,6 +67863,21 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BA251" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BB251" t="inlineStr">
+        <is>
+          <t>2error</t>
+        </is>
+      </c>
+      <c r="BC251" t="inlineStr">
+        <is>
+          <t>2error</t>
+        </is>
+      </c>
     </row>
     <row r="252">
       <c r="A252" t="inlineStr">
@@ -64265,6 +68034,21 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BA252" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BB252" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BC252" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="253">
       <c r="A253" t="inlineStr">
@@ -64419,6 +68203,21 @@
       <c r="AZ253" t="inlineStr">
         <is>
           <t>online</t>
+        </is>
+      </c>
+      <c r="BA253" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BB253" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BC253" t="inlineStr">
+        <is>
+          <t>1error</t>
         </is>
       </c>
     </row>
@@ -64497,6 +68296,21 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BA254" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BB254" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BC254" t="inlineStr">
+        <is>
+          <t>2error</t>
+        </is>
+      </c>
     </row>
     <row r="255">
       <c r="A255" t="inlineStr">
@@ -64573,6 +68387,21 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BA255" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BB255" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BC255" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="256">
       <c r="A256" t="inlineStr">
@@ -64649,6 +68478,21 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BA256" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BB256" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BC256" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="257">
       <c r="A257" t="inlineStr">
@@ -64725,6 +68569,21 @@
           <t>2error</t>
         </is>
       </c>
+      <c r="BA257" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BB257" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BC257" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="258">
       <c r="A258" t="inlineStr">
@@ -64801,6 +68660,21 @@
           <t>1error</t>
         </is>
       </c>
+      <c r="BA258" t="inlineStr">
+        <is>
+          <t>1error</t>
+        </is>
+      </c>
+      <c r="BB258" t="inlineStr">
+        <is>
+          <t>1error</t>
+        </is>
+      </c>
+      <c r="BC258" t="inlineStr">
+        <is>
+          <t>1error</t>
+        </is>
+      </c>
     </row>
     <row r="259">
       <c r="A259" t="inlineStr">
@@ -64877,6 +68751,21 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BA259" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BB259" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BC259" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/UATtracking.xlsx
+++ b/UATtracking.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BC259"/>
+  <dimension ref="A1:BH259"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -704,6 +704,31 @@
           <t>0113</t>
         </is>
       </c>
+      <c r="BD1" s="1" t="inlineStr">
+        <is>
+          <t>0114</t>
+        </is>
+      </c>
+      <c r="BE1" s="1" t="inlineStr">
+        <is>
+          <t>0115</t>
+        </is>
+      </c>
+      <c r="BF1" s="1" t="inlineStr">
+        <is>
+          <t>0116</t>
+        </is>
+      </c>
+      <c r="BG1" s="1" t="inlineStr">
+        <is>
+          <t>0117</t>
+        </is>
+      </c>
+      <c r="BH1" s="1" t="inlineStr">
+        <is>
+          <t>0120</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -975,6 +1000,31 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BD2" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BE2" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BF2" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BG2" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BH2" t="inlineStr">
+        <is>
+          <t>2error</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -1246,6 +1296,31 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BD3" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BE3" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BF3" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BG3" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BH3" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -1517,6 +1592,31 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BD4" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BE4" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BF4" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BG4" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BH4" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -1788,6 +1888,31 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BD5" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BE5" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BF5" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BG5" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BH5" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -2059,6 +2184,31 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BD6" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BE6" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BF6" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BG6" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BH6" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -2330,6 +2480,31 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BD7" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BE7" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BF7" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BG7" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BH7" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -2601,6 +2776,31 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BD8" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BE8" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BF8" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BG8" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BH8" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -2872,6 +3072,31 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BD9" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BE9" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BF9" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BG9" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BH9" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -3143,6 +3368,31 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BD10" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BE10" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BF10" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BG10" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BH10" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -3414,6 +3664,31 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BD11" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BE11" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BF11" t="inlineStr">
+        <is>
+          <t>1error</t>
+        </is>
+      </c>
+      <c r="BG11" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BH11" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -3685,6 +3960,31 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BD12" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BE12" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BF12" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BG12" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BH12" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -3956,6 +4256,31 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BD13" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BE13" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BF13" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BG13" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BH13" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -4227,6 +4552,31 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BD14" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BE14" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BF14" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BG14" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BH14" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -4498,6 +4848,31 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BD15" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BE15" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BF15" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BG15" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BH15" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -4769,6 +5144,31 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BD16" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BE16" t="inlineStr">
+        <is>
+          <t>1error</t>
+        </is>
+      </c>
+      <c r="BF16" t="inlineStr">
+        <is>
+          <t>1error</t>
+        </is>
+      </c>
+      <c r="BG16" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BH16" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -5040,6 +5440,31 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BD17" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BE17" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BF17" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BG17" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BH17" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -5311,6 +5736,31 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BD18" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BE18" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BF18" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BG18" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BH18" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -5582,6 +6032,31 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BD19" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BE19" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BF19" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BG19" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BH19" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -5853,6 +6328,31 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BD20" t="inlineStr">
+        <is>
+          <t>1error</t>
+        </is>
+      </c>
+      <c r="BE20" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BF20" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BG20" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BH20" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -6124,6 +6624,31 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BD21" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BE21" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BF21" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BG21" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BH21" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -6395,6 +6920,31 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BD22" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BE22" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BF22" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BG22" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BH22" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -6666,6 +7216,31 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BD23" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BE23" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BF23" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BG23" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BH23" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -6937,6 +7512,31 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BD24" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BE24" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BF24" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BG24" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BH24" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -7208,6 +7808,31 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BD25" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BE25" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BF25" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BG25" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BH25" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -7479,6 +8104,31 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BD26" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BE26" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BF26" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BG26" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BH26" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -7750,6 +8400,31 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BD27" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BE27" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BF27" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BG27" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BH27" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -8021,6 +8696,31 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BD28" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BE28" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BF28" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BG28" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BH28" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -8292,6 +8992,31 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BD29" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BE29" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BF29" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BG29" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BH29" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -8563,6 +9288,31 @@
           <t>2error</t>
         </is>
       </c>
+      <c r="BD30" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BE30" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BF30" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BG30" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BH30" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -8834,6 +9584,31 @@
           <t>1error</t>
         </is>
       </c>
+      <c r="BD31" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BE31" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BF31" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BG31" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BH31" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -9105,6 +9880,31 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BD32" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BE32" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BF32" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BG32" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BH32" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -9376,6 +10176,31 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BD33" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BE33" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BF33" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BG33" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BH33" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -9647,6 +10472,31 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BD34" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BE34" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BF34" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BG34" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BH34" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -9916,6 +10766,31 @@
           <t>offline</t>
         </is>
       </c>
+      <c r="BD35" t="inlineStr">
+        <is>
+          <t>offline</t>
+        </is>
+      </c>
+      <c r="BE35" t="inlineStr">
+        <is>
+          <t>offline</t>
+        </is>
+      </c>
+      <c r="BF35" t="inlineStr">
+        <is>
+          <t>offline</t>
+        </is>
+      </c>
+      <c r="BG35" t="inlineStr">
+        <is>
+          <t>offline</t>
+        </is>
+      </c>
+      <c r="BH35" t="inlineStr">
+        <is>
+          <t>offline</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -10187,6 +11062,31 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BD36" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BE36" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BF36" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BG36" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BH36" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -10458,6 +11358,31 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BD37" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BE37" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BF37" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BG37" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BH37" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -10729,6 +11654,31 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BD38" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BE38" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BF38" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BG38" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BH38" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -11000,6 +11950,31 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BD39" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BE39" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BF39" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BG39" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BH39" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -11271,6 +12246,31 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BD40" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BE40" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BF40" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BG40" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BH40" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -11542,6 +12542,31 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BD41" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BE41" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BF41" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BG41" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BH41" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -11813,6 +12838,31 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BD42" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BE42" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BF42" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BG42" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BH42" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -12084,6 +13134,31 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BD43" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BE43" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BF43" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BG43" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BH43" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -12355,6 +13430,31 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BD44" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BE44" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BF44" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BG44" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BH44" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -12626,6 +13726,31 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BD45" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BE45" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BF45" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BG45" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BH45" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -12897,6 +14022,31 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BD46" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BE46" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BF46" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BG46" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BH46" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -13168,6 +14318,31 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BD47" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BE47" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BF47" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BG47" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BH47" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -13439,6 +14614,31 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BD48" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BE48" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BF48" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BG48" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BH48" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -13710,6 +14910,31 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BD49" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BE49" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BF49" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BG49" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BH49" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -13981,6 +15206,31 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BD50" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BE50" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BF50" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BG50" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BH50" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -14252,6 +15502,31 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BD51" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BE51" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BF51" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BG51" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BH51" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -14523,6 +15798,31 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BD52" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BE52" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BF52" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BG52" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BH52" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -14792,6 +16092,31 @@
           <t>offline</t>
         </is>
       </c>
+      <c r="BD53" t="inlineStr">
+        <is>
+          <t>offline</t>
+        </is>
+      </c>
+      <c r="BE53" t="inlineStr">
+        <is>
+          <t>offline</t>
+        </is>
+      </c>
+      <c r="BF53" t="inlineStr">
+        <is>
+          <t>offline</t>
+        </is>
+      </c>
+      <c r="BG53" t="inlineStr">
+        <is>
+          <t>offline</t>
+        </is>
+      </c>
+      <c r="BH53" t="inlineStr">
+        <is>
+          <t>offline</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -15061,6 +16386,31 @@
           <t>offline</t>
         </is>
       </c>
+      <c r="BD54" t="inlineStr">
+        <is>
+          <t>offline</t>
+        </is>
+      </c>
+      <c r="BE54" t="inlineStr">
+        <is>
+          <t>offline</t>
+        </is>
+      </c>
+      <c r="BF54" t="inlineStr">
+        <is>
+          <t>offline</t>
+        </is>
+      </c>
+      <c r="BG54" t="inlineStr">
+        <is>
+          <t>offline</t>
+        </is>
+      </c>
+      <c r="BH54" t="inlineStr">
+        <is>
+          <t>offline</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -15332,6 +16682,31 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BD55" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BE55" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BF55" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BG55" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BH55" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -15603,6 +16978,31 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BD56" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BE56" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BF56" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BG56" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BH56" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -15874,6 +17274,31 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BD57" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BE57" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BF57" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BG57" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BH57" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -16145,6 +17570,31 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BD58" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BE58" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BF58" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BG58" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BH58" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -16416,6 +17866,31 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BD59" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BE59" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BF59" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BG59" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BH59" t="inlineStr">
+        <is>
+          <t>1error</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -16687,6 +18162,31 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BD60" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BE60" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BF60" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BG60" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BH60" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -16958,6 +18458,31 @@
           <t>1error</t>
         </is>
       </c>
+      <c r="BD61" t="inlineStr">
+        <is>
+          <t>1error</t>
+        </is>
+      </c>
+      <c r="BE61" t="inlineStr">
+        <is>
+          <t>1error</t>
+        </is>
+      </c>
+      <c r="BF61" t="inlineStr">
+        <is>
+          <t>2error</t>
+        </is>
+      </c>
+      <c r="BG61" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BH61" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -17229,6 +18754,31 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BD62" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BE62" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BF62" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BG62" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BH62" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -17500,6 +19050,31 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BD63" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BE63" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BF63" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BG63" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BH63" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -17771,6 +19346,31 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BD64" t="inlineStr">
+        <is>
+          <t>1error</t>
+        </is>
+      </c>
+      <c r="BE64" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BF64" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BG64" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BH64" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -18042,6 +19642,31 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BD65" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BE65" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BF65" t="inlineStr">
+        <is>
+          <t>1error</t>
+        </is>
+      </c>
+      <c r="BG65" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BH65" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -18313,6 +19938,31 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BD66" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BE66" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BF66" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BG66" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BH66" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -18584,6 +20234,31 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BD67" t="inlineStr">
+        <is>
+          <t>1error</t>
+        </is>
+      </c>
+      <c r="BE67" t="inlineStr">
+        <is>
+          <t>1error</t>
+        </is>
+      </c>
+      <c r="BF67" t="inlineStr">
+        <is>
+          <t>1error</t>
+        </is>
+      </c>
+      <c r="BG67" t="inlineStr">
+        <is>
+          <t>1error</t>
+        </is>
+      </c>
+      <c r="BH67" t="inlineStr">
+        <is>
+          <t>1error</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -18855,6 +20530,31 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BD68" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BE68" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BF68" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BG68" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BH68" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -19126,6 +20826,31 @@
           <t>2error</t>
         </is>
       </c>
+      <c r="BD69" t="inlineStr">
+        <is>
+          <t>2error</t>
+        </is>
+      </c>
+      <c r="BE69" t="inlineStr">
+        <is>
+          <t>2error</t>
+        </is>
+      </c>
+      <c r="BF69" t="inlineStr">
+        <is>
+          <t>2error</t>
+        </is>
+      </c>
+      <c r="BG69" t="inlineStr">
+        <is>
+          <t>2error</t>
+        </is>
+      </c>
+      <c r="BH69" t="inlineStr">
+        <is>
+          <t>2error</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -19397,6 +21122,31 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BD70" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BE70" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BF70" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BG70" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BH70" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -19668,6 +21418,31 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BD71" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BE71" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BF71" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BG71" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BH71" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -19939,6 +21714,31 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BD72" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BE72" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BF72" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BG72" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BH72" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -20210,6 +22010,31 @@
           <t>2error</t>
         </is>
       </c>
+      <c r="BD73" t="inlineStr">
+        <is>
+          <t>2error</t>
+        </is>
+      </c>
+      <c r="BE73" t="inlineStr">
+        <is>
+          <t>2error</t>
+        </is>
+      </c>
+      <c r="BF73" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BG73" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BH73" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -20481,6 +22306,31 @@
           <t>1error</t>
         </is>
       </c>
+      <c r="BD74" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BE74" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BF74" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BG74" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BH74" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -20752,6 +22602,31 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BD75" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BE75" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BF75" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BG75" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BH75" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -21023,6 +22898,31 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BD76" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BE76" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BF76" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BG76" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BH76" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
@@ -21294,6 +23194,31 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BD77" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BE77" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BF77" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BG77" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BH77" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
@@ -21565,6 +23490,31 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BD78" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BE78" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BF78" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BG78" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BH78" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
@@ -21836,6 +23786,31 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BD79" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BE79" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BF79" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BG79" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BH79" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
@@ -22105,6 +24080,31 @@
           <t>offline</t>
         </is>
       </c>
+      <c r="BD80" t="inlineStr">
+        <is>
+          <t>offline</t>
+        </is>
+      </c>
+      <c r="BE80" t="inlineStr">
+        <is>
+          <t>offline</t>
+        </is>
+      </c>
+      <c r="BF80" t="inlineStr">
+        <is>
+          <t>offline</t>
+        </is>
+      </c>
+      <c r="BG80" t="inlineStr">
+        <is>
+          <t>offline</t>
+        </is>
+      </c>
+      <c r="BH80" t="inlineStr">
+        <is>
+          <t>offline</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
@@ -22376,6 +24376,31 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BD81" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BE81" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BF81" t="inlineStr">
+        <is>
+          <t>2error</t>
+        </is>
+      </c>
+      <c r="BG81" t="inlineStr">
+        <is>
+          <t>2error</t>
+        </is>
+      </c>
+      <c r="BH81" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
@@ -22647,6 +24672,31 @@
           <t>1error</t>
         </is>
       </c>
+      <c r="BD82" t="inlineStr">
+        <is>
+          <t>1error</t>
+        </is>
+      </c>
+      <c r="BE82" t="inlineStr">
+        <is>
+          <t>1error</t>
+        </is>
+      </c>
+      <c r="BF82" t="inlineStr">
+        <is>
+          <t>1error</t>
+        </is>
+      </c>
+      <c r="BG82" t="inlineStr">
+        <is>
+          <t>1error</t>
+        </is>
+      </c>
+      <c r="BH82" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
@@ -22918,6 +24968,31 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BD83" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BE83" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BF83" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BG83" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BH83" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
@@ -23189,6 +25264,31 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BD84" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BE84" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BF84" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BG84" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BH84" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
@@ -23460,6 +25560,31 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BD85" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BE85" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BF85" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BG85" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BH85" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
@@ -23731,6 +25856,31 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BD86" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BE86" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BF86" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BG86" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BH86" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
@@ -24002,6 +26152,31 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BD87" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BE87" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BF87" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BG87" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BH87" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
@@ -24273,6 +26448,31 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BD88" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BE88" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BF88" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BG88" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BH88" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
@@ -24544,6 +26744,31 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BD89" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BE89" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BF89" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BG89" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BH89" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
@@ -24815,6 +27040,31 @@
           <t>2error</t>
         </is>
       </c>
+      <c r="BD90" t="inlineStr">
+        <is>
+          <t>2error</t>
+        </is>
+      </c>
+      <c r="BE90" t="inlineStr">
+        <is>
+          <t>2error</t>
+        </is>
+      </c>
+      <c r="BF90" t="inlineStr">
+        <is>
+          <t>2error</t>
+        </is>
+      </c>
+      <c r="BG90" t="inlineStr">
+        <is>
+          <t>2error</t>
+        </is>
+      </c>
+      <c r="BH90" t="inlineStr">
+        <is>
+          <t>2error</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
@@ -25086,6 +27336,31 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BD91" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BE91" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BF91" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BG91" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BH91" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
@@ -25357,6 +27632,31 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BD92" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BE92" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BF92" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BG92" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BH92" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
@@ -25628,6 +27928,31 @@
           <t>1error</t>
         </is>
       </c>
+      <c r="BD93" t="inlineStr">
+        <is>
+          <t>1error</t>
+        </is>
+      </c>
+      <c r="BE93" t="inlineStr">
+        <is>
+          <t>1error</t>
+        </is>
+      </c>
+      <c r="BF93" t="inlineStr">
+        <is>
+          <t>1error</t>
+        </is>
+      </c>
+      <c r="BG93" t="inlineStr">
+        <is>
+          <t>1error</t>
+        </is>
+      </c>
+      <c r="BH93" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
@@ -25899,6 +28224,31 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BD94" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BE94" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BF94" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BG94" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BH94" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
@@ -26170,6 +28520,31 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BD95" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BE95" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BF95" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BG95" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BH95" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
@@ -26441,6 +28816,31 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BD96" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BE96" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BF96" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BG96" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BH96" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
@@ -26712,6 +29112,31 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BD97" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BE97" t="inlineStr">
+        <is>
+          <t>offline</t>
+        </is>
+      </c>
+      <c r="BF97" t="inlineStr">
+        <is>
+          <t>offline</t>
+        </is>
+      </c>
+      <c r="BG97" t="inlineStr">
+        <is>
+          <t>offline</t>
+        </is>
+      </c>
+      <c r="BH97" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
@@ -26983,6 +29408,31 @@
           <t>2error</t>
         </is>
       </c>
+      <c r="BD98" t="inlineStr">
+        <is>
+          <t>2error</t>
+        </is>
+      </c>
+      <c r="BE98" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BF98" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BG98" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BH98" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
@@ -26994,10 +29444,8 @@
       <c r="C99" t="n">
         <v>2</v>
       </c>
-      <c r="D99" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="D99" t="n">
+        <v>2</v>
       </c>
       <c r="E99" t="inlineStr">
         <is>
@@ -27252,6 +29700,31 @@
       <c r="BC99" t="inlineStr">
         <is>
           <t>online</t>
+        </is>
+      </c>
+      <c r="BD99" t="inlineStr">
+        <is>
+          <t>offline</t>
+        </is>
+      </c>
+      <c r="BE99" t="inlineStr">
+        <is>
+          <t>offline</t>
+        </is>
+      </c>
+      <c r="BF99" t="inlineStr">
+        <is>
+          <t>offline</t>
+        </is>
+      </c>
+      <c r="BG99" t="inlineStr">
+        <is>
+          <t>offline</t>
+        </is>
+      </c>
+      <c r="BH99" t="inlineStr">
+        <is>
+          <t>offline</t>
         </is>
       </c>
     </row>
@@ -27525,6 +29998,31 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BD100" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BE100" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BF100" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BG100" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BH100" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
@@ -27796,6 +30294,31 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BD101" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BE101" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BF101" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BG101" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BH101" t="inlineStr">
+        <is>
+          <t>1error</t>
+        </is>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
@@ -28067,6 +30590,31 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BD102" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BE102" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BF102" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BG102" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BH102" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
@@ -28338,6 +30886,31 @@
           <t>1error</t>
         </is>
       </c>
+      <c r="BD103" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BE103" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BF103" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BG103" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BH103" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
@@ -28609,6 +31182,31 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BD104" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BE104" t="inlineStr">
+        <is>
+          <t>1error</t>
+        </is>
+      </c>
+      <c r="BF104" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BG104" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BH104" t="inlineStr">
+        <is>
+          <t>2error</t>
+        </is>
+      </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
@@ -28880,6 +31478,31 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BD105" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BE105" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BF105" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BG105" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BH105" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
@@ -29151,6 +31774,31 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BD106" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BE106" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BF106" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BG106" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BH106" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
@@ -29164,7 +31812,7 @@
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
@@ -29418,6 +32066,31 @@
         </is>
       </c>
       <c r="BC107" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BD107" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BE107" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BF107" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BG107" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BH107" t="inlineStr">
         <is>
           <t>online</t>
         </is>
@@ -29693,6 +32366,31 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BD108" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BE108" t="inlineStr">
+        <is>
+          <t>1error</t>
+        </is>
+      </c>
+      <c r="BF108" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BG108" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BH108" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
@@ -29964,6 +32662,31 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BD109" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BE109" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BF109" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BG109" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BH109" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
@@ -30235,6 +32958,31 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BD110" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BE110" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BF110" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BG110" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BH110" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
@@ -30506,6 +33254,31 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BD111" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BE111" t="inlineStr">
+        <is>
+          <t>1error</t>
+        </is>
+      </c>
+      <c r="BF111" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BG111" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BH111" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
@@ -30777,6 +33550,31 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BD112" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BE112" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BF112" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BG112" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BH112" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
@@ -31048,6 +33846,31 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BD113" t="inlineStr">
+        <is>
+          <t>1error</t>
+        </is>
+      </c>
+      <c r="BE113" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BF113" t="inlineStr">
+        <is>
+          <t>1error</t>
+        </is>
+      </c>
+      <c r="BG113" t="inlineStr">
+        <is>
+          <t>1error</t>
+        </is>
+      </c>
+      <c r="BH113" t="inlineStr">
+        <is>
+          <t>1error</t>
+        </is>
+      </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
@@ -31319,6 +34142,31 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BD114" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BE114" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BF114" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BG114" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BH114" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
@@ -31590,6 +34438,31 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BD115" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BE115" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BF115" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BG115" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BH115" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
@@ -31861,6 +34734,31 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BD116" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BE116" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BF116" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BG116" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BH116" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
@@ -31872,10 +34770,8 @@
       <c r="C117" t="n">
         <v>2</v>
       </c>
-      <c r="D117" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="D117" t="n">
+        <v>2</v>
       </c>
       <c r="E117" t="inlineStr">
         <is>
@@ -32130,6 +35026,31 @@
       <c r="BC117" t="inlineStr">
         <is>
           <t>1error</t>
+        </is>
+      </c>
+      <c r="BD117" t="inlineStr">
+        <is>
+          <t>1error</t>
+        </is>
+      </c>
+      <c r="BE117" t="inlineStr">
+        <is>
+          <t>1error</t>
+        </is>
+      </c>
+      <c r="BF117" t="inlineStr">
+        <is>
+          <t>offline</t>
+        </is>
+      </c>
+      <c r="BG117" t="inlineStr">
+        <is>
+          <t>offline</t>
+        </is>
+      </c>
+      <c r="BH117" t="inlineStr">
+        <is>
+          <t>offline</t>
         </is>
       </c>
     </row>
@@ -32403,6 +35324,31 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BD118" t="inlineStr">
+        <is>
+          <t>1error</t>
+        </is>
+      </c>
+      <c r="BE118" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BF118" t="inlineStr">
+        <is>
+          <t>1error</t>
+        </is>
+      </c>
+      <c r="BG118" t="inlineStr">
+        <is>
+          <t>1error</t>
+        </is>
+      </c>
+      <c r="BH118" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
@@ -32672,6 +35618,31 @@
           <t>offline</t>
         </is>
       </c>
+      <c r="BD119" t="inlineStr">
+        <is>
+          <t>offline</t>
+        </is>
+      </c>
+      <c r="BE119" t="inlineStr">
+        <is>
+          <t>offline</t>
+        </is>
+      </c>
+      <c r="BF119" t="inlineStr">
+        <is>
+          <t>offline</t>
+        </is>
+      </c>
+      <c r="BG119" t="inlineStr">
+        <is>
+          <t>offline</t>
+        </is>
+      </c>
+      <c r="BH119" t="inlineStr">
+        <is>
+          <t>offline</t>
+        </is>
+      </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
@@ -32943,6 +35914,31 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BD120" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BE120" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BF120" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BG120" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BH120" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
@@ -33214,6 +36210,31 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BD121" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BE121" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BF121" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BG121" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BH121" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
@@ -33485,6 +36506,31 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BD122" t="inlineStr">
+        <is>
+          <t>1error</t>
+        </is>
+      </c>
+      <c r="BE122" t="inlineStr">
+        <is>
+          <t>1error</t>
+        </is>
+      </c>
+      <c r="BF122" t="inlineStr">
+        <is>
+          <t>1error</t>
+        </is>
+      </c>
+      <c r="BG122" t="inlineStr">
+        <is>
+          <t>1error</t>
+        </is>
+      </c>
+      <c r="BH122" t="inlineStr">
+        <is>
+          <t>1error</t>
+        </is>
+      </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
@@ -33756,6 +36802,31 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BD123" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BE123" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BF123" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BG123" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BH123" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
@@ -34027,6 +37098,31 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BD124" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BE124" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BF124" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BG124" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BH124" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
@@ -34298,6 +37394,31 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BD125" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BE125" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BF125" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BG125" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BH125" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
@@ -34567,6 +37688,31 @@
           <t>offline</t>
         </is>
       </c>
+      <c r="BD126" t="inlineStr">
+        <is>
+          <t>offline</t>
+        </is>
+      </c>
+      <c r="BE126" t="inlineStr">
+        <is>
+          <t>offline</t>
+        </is>
+      </c>
+      <c r="BF126" t="inlineStr">
+        <is>
+          <t>offline</t>
+        </is>
+      </c>
+      <c r="BG126" t="inlineStr">
+        <is>
+          <t>offline</t>
+        </is>
+      </c>
+      <c r="BH126" t="inlineStr">
+        <is>
+          <t>offline</t>
+        </is>
+      </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
@@ -34838,6 +37984,31 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BD127" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BE127" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BF127" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BG127" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BH127" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
@@ -35109,6 +38280,31 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BD128" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BE128" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BF128" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BG128" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BH128" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
@@ -35380,6 +38576,31 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BD129" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BE129" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BF129" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BG129" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BH129" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
@@ -35651,6 +38872,31 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BD130" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BE130" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BF130" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BG130" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BH130" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
@@ -35922,6 +39168,31 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BD131" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BE131" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BF131" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BG131" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BH131" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
@@ -36193,6 +39464,31 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BD132" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BE132" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BF132" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BG132" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BH132" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
@@ -36462,6 +39758,31 @@
           <t>offline</t>
         </is>
       </c>
+      <c r="BD133" t="inlineStr">
+        <is>
+          <t>offline</t>
+        </is>
+      </c>
+      <c r="BE133" t="inlineStr">
+        <is>
+          <t>offline</t>
+        </is>
+      </c>
+      <c r="BF133" t="inlineStr">
+        <is>
+          <t>offline</t>
+        </is>
+      </c>
+      <c r="BG133" t="inlineStr">
+        <is>
+          <t>offline</t>
+        </is>
+      </c>
+      <c r="BH133" t="inlineStr">
+        <is>
+          <t>offline</t>
+        </is>
+      </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
@@ -36733,6 +40054,31 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BD134" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BE134" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BF134" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BG134" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BH134" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
@@ -37004,6 +40350,31 @@
           <t>1error</t>
         </is>
       </c>
+      <c r="BD135" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BE135" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BF135" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BG135" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BH135" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
@@ -37017,7 +40388,7 @@
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="E136" t="inlineStr">
@@ -37273,6 +40644,31 @@
       <c r="BC136" t="inlineStr">
         <is>
           <t>1error</t>
+        </is>
+      </c>
+      <c r="BD136" t="inlineStr">
+        <is>
+          <t>offline</t>
+        </is>
+      </c>
+      <c r="BE136" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BF136" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BG136" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BH136" t="inlineStr">
+        <is>
+          <t>online</t>
         </is>
       </c>
     </row>
@@ -37546,6 +40942,31 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BD137" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BE137" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BF137" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BG137" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BH137" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
@@ -37815,6 +41236,31 @@
           <t>offline</t>
         </is>
       </c>
+      <c r="BD138" t="inlineStr">
+        <is>
+          <t>offline</t>
+        </is>
+      </c>
+      <c r="BE138" t="inlineStr">
+        <is>
+          <t>offline</t>
+        </is>
+      </c>
+      <c r="BF138" t="inlineStr">
+        <is>
+          <t>offline</t>
+        </is>
+      </c>
+      <c r="BG138" t="inlineStr">
+        <is>
+          <t>offline</t>
+        </is>
+      </c>
+      <c r="BH138" t="inlineStr">
+        <is>
+          <t>offline</t>
+        </is>
+      </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
@@ -38086,6 +41532,31 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BD139" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BE139" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BF139" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BG139" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BH139" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
@@ -38357,6 +41828,31 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BD140" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BE140" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BF140" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BG140" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BH140" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
@@ -38628,6 +42124,31 @@
           <t>1error</t>
         </is>
       </c>
+      <c r="BD141" t="inlineStr">
+        <is>
+          <t>1error</t>
+        </is>
+      </c>
+      <c r="BE141" t="inlineStr">
+        <is>
+          <t>1error</t>
+        </is>
+      </c>
+      <c r="BF141" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BG141" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BH141" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
@@ -38899,6 +42420,31 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BD142" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BE142" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BF142" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BG142" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BH142" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
@@ -39170,6 +42716,31 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BD143" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BE143" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BF143" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BG143" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BH143" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
@@ -39441,6 +43012,31 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BD144" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BE144" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BF144" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BG144" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BH144" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
@@ -39712,6 +43308,31 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BD145" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BE145" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BF145" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BG145" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BH145" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
@@ -39983,6 +43604,31 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BD146" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BE146" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BF146" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BG146" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BH146" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
@@ -40254,6 +43900,31 @@
           <t>2error</t>
         </is>
       </c>
+      <c r="BD147" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BE147" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BF147" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BG147" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BH147" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
@@ -40525,6 +44196,31 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BD148" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BE148" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BF148" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BG148" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BH148" t="inlineStr">
+        <is>
+          <t>1error</t>
+        </is>
+      </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
@@ -40796,6 +44492,31 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BD149" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BE149" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BF149" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BG149" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BH149" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
@@ -41067,6 +44788,31 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BD150" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BE150" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BF150" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BG150" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BH150" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
@@ -41338,6 +45084,31 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BD151" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BE151" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BF151" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BG151" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BH151" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
@@ -41607,6 +45378,31 @@
           <t>offline</t>
         </is>
       </c>
+      <c r="BD152" t="inlineStr">
+        <is>
+          <t>offline</t>
+        </is>
+      </c>
+      <c r="BE152" t="inlineStr">
+        <is>
+          <t>offline</t>
+        </is>
+      </c>
+      <c r="BF152" t="inlineStr">
+        <is>
+          <t>offline</t>
+        </is>
+      </c>
+      <c r="BG152" t="inlineStr">
+        <is>
+          <t>offline</t>
+        </is>
+      </c>
+      <c r="BH152" t="inlineStr">
+        <is>
+          <t>offline</t>
+        </is>
+      </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
@@ -41620,7 +45416,7 @@
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="E153" t="inlineStr">
@@ -41874,6 +45670,31 @@
         </is>
       </c>
       <c r="BC153" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BD153" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BE153" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BF153" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BG153" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BH153" t="inlineStr">
         <is>
           <t>online</t>
         </is>
@@ -42149,6 +45970,31 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BD154" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BE154" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BF154" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BG154" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BH154" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
@@ -42420,6 +46266,31 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BD155" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BE155" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BF155" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BG155" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BH155" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
@@ -42691,6 +46562,31 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BD156" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BE156" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BF156" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BG156" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BH156" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
@@ -42962,6 +46858,31 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BD157" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BE157" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BF157" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BG157" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BH157" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
@@ -43233,6 +47154,31 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BD158" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BE158" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BF158" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BG158" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BH158" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
@@ -43504,6 +47450,31 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BD159" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BE159" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BF159" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BG159" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BH159" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
@@ -43775,6 +47746,31 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BD160" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BE160" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BF160" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BG160" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BH160" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
@@ -44046,6 +48042,31 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BD161" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BE161" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BF161" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BG161" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BH161" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
@@ -44317,6 +48338,31 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BD162" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BE162" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BF162" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BG162" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BH162" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
@@ -44588,6 +48634,31 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BD163" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BE163" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BF163" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BG163" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BH163" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
@@ -44859,6 +48930,31 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BD164" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BE164" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BF164" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BG164" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BH164" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
@@ -45130,6 +49226,31 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BD165" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BE165" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BF165" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BG165" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BH165" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
@@ -45401,6 +49522,31 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BD166" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BE166" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BF166" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BG166" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BH166" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
@@ -45672,6 +49818,31 @@
           <t>1error</t>
         </is>
       </c>
+      <c r="BD167" t="inlineStr">
+        <is>
+          <t>1error</t>
+        </is>
+      </c>
+      <c r="BE167" t="inlineStr">
+        <is>
+          <t>1error</t>
+        </is>
+      </c>
+      <c r="BF167" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BG167" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BH167" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
@@ -45683,10 +49854,8 @@
       <c r="C168" t="n">
         <v>2</v>
       </c>
-      <c r="D168" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="D168" t="n">
+        <v>2</v>
       </c>
       <c r="E168" t="inlineStr">
         <is>
@@ -45941,6 +50110,31 @@
       <c r="BC168" t="inlineStr">
         <is>
           <t>online</t>
+        </is>
+      </c>
+      <c r="BD168" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BE168" t="inlineStr">
+        <is>
+          <t>offline</t>
+        </is>
+      </c>
+      <c r="BF168" t="inlineStr">
+        <is>
+          <t>offline</t>
+        </is>
+      </c>
+      <c r="BG168" t="inlineStr">
+        <is>
+          <t>offline</t>
+        </is>
+      </c>
+      <c r="BH168" t="inlineStr">
+        <is>
+          <t>offline</t>
         </is>
       </c>
     </row>
@@ -46214,6 +50408,31 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BD169" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BE169" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BF169" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BG169" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BH169" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
@@ -46485,6 +50704,31 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BD170" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BE170" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BF170" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BG170" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BH170" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
@@ -46756,6 +51000,31 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BD171" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BE171" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BF171" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BG171" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BH171" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
@@ -47027,6 +51296,31 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BD172" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BE172" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BF172" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BG172" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BH172" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
@@ -47298,6 +51592,31 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BD173" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BE173" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BF173" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BG173" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BH173" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
@@ -47569,6 +51888,31 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BD174" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BE174" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BF174" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BG174" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BH174" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
@@ -47840,6 +52184,31 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BD175" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BE175" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BF175" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BG175" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BH175" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
@@ -48111,6 +52480,31 @@
           <t>1error</t>
         </is>
       </c>
+      <c r="BD176" t="inlineStr">
+        <is>
+          <t>1error</t>
+        </is>
+      </c>
+      <c r="BE176" t="inlineStr">
+        <is>
+          <t>1error</t>
+        </is>
+      </c>
+      <c r="BF176" t="inlineStr">
+        <is>
+          <t>1error</t>
+        </is>
+      </c>
+      <c r="BG176" t="inlineStr">
+        <is>
+          <t>1error</t>
+        </is>
+      </c>
+      <c r="BH176" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
@@ -48380,6 +52774,31 @@
           <t>offline</t>
         </is>
       </c>
+      <c r="BD177" t="inlineStr">
+        <is>
+          <t>offline</t>
+        </is>
+      </c>
+      <c r="BE177" t="inlineStr">
+        <is>
+          <t>offline</t>
+        </is>
+      </c>
+      <c r="BF177" t="inlineStr">
+        <is>
+          <t>offline</t>
+        </is>
+      </c>
+      <c r="BG177" t="inlineStr">
+        <is>
+          <t>offline</t>
+        </is>
+      </c>
+      <c r="BH177" t="inlineStr">
+        <is>
+          <t>offline</t>
+        </is>
+      </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
@@ -48651,6 +53070,31 @@
           <t>1error</t>
         </is>
       </c>
+      <c r="BD178" t="inlineStr">
+        <is>
+          <t>1error</t>
+        </is>
+      </c>
+      <c r="BE178" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BF178" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BG178" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BH178" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
@@ -48922,6 +53366,31 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BD179" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BE179" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BF179" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BG179" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BH179" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
@@ -49193,6 +53662,31 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BD180" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BE180" t="inlineStr">
+        <is>
+          <t>offline</t>
+        </is>
+      </c>
+      <c r="BF180" t="inlineStr">
+        <is>
+          <t>offline</t>
+        </is>
+      </c>
+      <c r="BG180" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BH180" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
@@ -49464,6 +53958,31 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BD181" t="inlineStr">
+        <is>
+          <t>2error</t>
+        </is>
+      </c>
+      <c r="BE181" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BF181" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BG181" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BH181" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
@@ -49733,6 +54252,31 @@
           <t>offline</t>
         </is>
       </c>
+      <c r="BD182" t="inlineStr">
+        <is>
+          <t>offline</t>
+        </is>
+      </c>
+      <c r="BE182" t="inlineStr">
+        <is>
+          <t>offline</t>
+        </is>
+      </c>
+      <c r="BF182" t="inlineStr">
+        <is>
+          <t>offline</t>
+        </is>
+      </c>
+      <c r="BG182" t="inlineStr">
+        <is>
+          <t>offline</t>
+        </is>
+      </c>
+      <c r="BH182" t="inlineStr">
+        <is>
+          <t>offline</t>
+        </is>
+      </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
@@ -49744,8 +54288,10 @@
       <c r="C183" t="n">
         <v>2</v>
       </c>
-      <c r="D183" t="n">
-        <v>2</v>
+      <c r="D183" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
       </c>
       <c r="E183" t="inlineStr">
         <is>
@@ -50000,6 +54546,31 @@
       <c r="BC183" t="inlineStr">
         <is>
           <t>offline</t>
+        </is>
+      </c>
+      <c r="BD183" t="inlineStr">
+        <is>
+          <t>offline</t>
+        </is>
+      </c>
+      <c r="BE183" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BF183" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BG183" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BH183" t="inlineStr">
+        <is>
+          <t>online</t>
         </is>
       </c>
     </row>
@@ -50273,6 +54844,31 @@
           <t>1error</t>
         </is>
       </c>
+      <c r="BD184" t="inlineStr">
+        <is>
+          <t>1error</t>
+        </is>
+      </c>
+      <c r="BE184" t="inlineStr">
+        <is>
+          <t>1error</t>
+        </is>
+      </c>
+      <c r="BF184" t="inlineStr">
+        <is>
+          <t>1error</t>
+        </is>
+      </c>
+      <c r="BG184" t="inlineStr">
+        <is>
+          <t>1error</t>
+        </is>
+      </c>
+      <c r="BH184" t="inlineStr">
+        <is>
+          <t>1error</t>
+        </is>
+      </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
@@ -50544,6 +55140,31 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BD185" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BE185" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BF185" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BG185" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BH185" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
@@ -50815,6 +55436,31 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BD186" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BE186" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BF186" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BG186" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BH186" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
@@ -51086,6 +55732,31 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BD187" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BE187" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BF187" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BG187" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BH187" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
@@ -51097,10 +55768,8 @@
       <c r="C188" t="n">
         <v>2</v>
       </c>
-      <c r="D188" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="D188" t="n">
+        <v>1</v>
       </c>
       <c r="E188" t="inlineStr">
         <is>
@@ -51355,6 +56024,31 @@
       <c r="BC188" t="inlineStr">
         <is>
           <t>online</t>
+        </is>
+      </c>
+      <c r="BD188" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BE188" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BF188" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BG188" t="inlineStr">
+        <is>
+          <t>offline</t>
+        </is>
+      </c>
+      <c r="BH188" t="inlineStr">
+        <is>
+          <t>offline</t>
         </is>
       </c>
     </row>
@@ -51628,6 +56322,31 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BD189" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BE189" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BF189" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BG189" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BH189" t="inlineStr">
+        <is>
+          <t>1error</t>
+        </is>
+      </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
@@ -51899,6 +56618,31 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BD190" t="inlineStr">
+        <is>
+          <t>1error</t>
+        </is>
+      </c>
+      <c r="BE190" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BF190" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BG190" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BH190" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
@@ -52170,6 +56914,31 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BD191" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BE191" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BF191" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BG191" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BH191" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
@@ -52441,6 +57210,31 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BD192" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BE192" t="inlineStr">
+        <is>
+          <t>1error</t>
+        </is>
+      </c>
+      <c r="BF192" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BG192" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BH192" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
@@ -52712,6 +57506,31 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BD193" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BE193" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BF193" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BG193" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BH193" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
@@ -52983,6 +57802,31 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BD194" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BE194" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BF194" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BG194" t="inlineStr">
+        <is>
+          <t>1error</t>
+        </is>
+      </c>
+      <c r="BH194" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
@@ -53254,6 +58098,31 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BD195" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BE195" t="inlineStr">
+        <is>
+          <t>1error</t>
+        </is>
+      </c>
+      <c r="BF195" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BG195" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BH195" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
@@ -53525,6 +58394,31 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BD196" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BE196" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BF196" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BG196" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BH196" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
@@ -53796,6 +58690,31 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BD197" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BE197" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BF197" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BG197" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BH197" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
@@ -54067,6 +58986,31 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BD198" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BE198" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BF198" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BG198" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BH198" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
@@ -54338,6 +59282,31 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BD199" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BE199" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BF199" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BG199" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BH199" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
@@ -54609,6 +59578,31 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BD200" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BE200" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BF200" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BG200" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BH200" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
@@ -54880,6 +59874,31 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BD201" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BE201" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BF201" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BG201" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BH201" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
@@ -55151,6 +60170,31 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BD202" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BE202" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BF202" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BG202" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BH202" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
@@ -55422,6 +60466,31 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BD203" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BE203" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BF203" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BG203" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BH203" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
@@ -55693,6 +60762,31 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BD204" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BE204" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BF204" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BG204" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BH204" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
@@ -55964,6 +61058,31 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BD205" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BE205" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BF205" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BG205" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BH205" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
@@ -56235,6 +61354,31 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BD206" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BE206" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BF206" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BG206" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BH206" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
@@ -56506,6 +61650,31 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BD207" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BE207" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BF207" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BG207" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BH207" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
@@ -56777,6 +61946,31 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BD208" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BE208" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BF208" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BG208" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BH208" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
@@ -57048,6 +62242,31 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BD209" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BE209" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BF209" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BG209" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BH209" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
@@ -57319,6 +62538,31 @@
           <t>1error</t>
         </is>
       </c>
+      <c r="BD210" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BE210" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BF210" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BG210" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BH210" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
@@ -57590,6 +62834,31 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BD211" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BE211" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BF211" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BG211" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BH211" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
@@ -57861,6 +63130,31 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BD212" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BE212" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BF212" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BG212" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BH212" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
@@ -58132,6 +63426,31 @@
           <t>1error</t>
         </is>
       </c>
+      <c r="BD213" t="inlineStr">
+        <is>
+          <t>1error</t>
+        </is>
+      </c>
+      <c r="BE213" t="inlineStr">
+        <is>
+          <t>1error</t>
+        </is>
+      </c>
+      <c r="BF213" t="inlineStr">
+        <is>
+          <t>1error</t>
+        </is>
+      </c>
+      <c r="BG213" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BH213" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
@@ -58403,6 +63722,31 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BD214" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BE214" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BF214" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BG214" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BH214" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
@@ -58674,6 +64018,31 @@
           <t>1error</t>
         </is>
       </c>
+      <c r="BD215" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BE215" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BF215" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BG215" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BH215" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
@@ -58945,6 +64314,31 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BD216" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BE216" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BF216" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BG216" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BH216" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
@@ -59216,6 +64610,31 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BD217" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BE217" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BF217" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BG217" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BH217" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
@@ -59487,6 +64906,31 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BD218" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BE218" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BF218" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BG218" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BH218" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
@@ -59758,6 +65202,31 @@
           <t>1error</t>
         </is>
       </c>
+      <c r="BD219" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BE219" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BF219" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BG219" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BH219" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
@@ -60029,6 +65498,31 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BD220" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BE220" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BF220" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BG220" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BH220" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="221">
       <c r="A221" t="inlineStr">
@@ -60300,6 +65794,31 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BD221" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BE221" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BF221" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BG221" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BH221" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="222">
       <c r="A222" t="inlineStr">
@@ -60571,6 +66090,31 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BD222" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BE222" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BF222" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BG222" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BH222" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr">
@@ -60842,6 +66386,31 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BD223" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BE223" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BF223" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BG223" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BH223" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="224">
       <c r="A224" t="inlineStr">
@@ -61113,6 +66682,31 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BD224" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BE224" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BF224" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BG224" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BH224" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="225">
       <c r="A225" t="inlineStr">
@@ -61384,6 +66978,31 @@
           <t>1error</t>
         </is>
       </c>
+      <c r="BD225" t="inlineStr">
+        <is>
+          <t>1error</t>
+        </is>
+      </c>
+      <c r="BE225" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BF225" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BG225" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BH225" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="226">
       <c r="A226" t="inlineStr">
@@ -61655,6 +67274,31 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BD226" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BE226" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BF226" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BG226" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BH226" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="227">
       <c r="A227" t="inlineStr">
@@ -61926,6 +67570,31 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BD227" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BE227" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BF227" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BG227" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BH227" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="228">
       <c r="A228" t="inlineStr">
@@ -62197,6 +67866,31 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BD228" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BE228" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BF228" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BG228" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BH228" t="inlineStr">
+        <is>
+          <t>1error</t>
+        </is>
+      </c>
     </row>
     <row r="229">
       <c r="A229" t="inlineStr">
@@ -62468,6 +68162,31 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BD229" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BE229" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BF229" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BG229" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BH229" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="230">
       <c r="A230" t="inlineStr">
@@ -62739,6 +68458,31 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BD230" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BE230" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BF230" t="inlineStr">
+        <is>
+          <t>1error</t>
+        </is>
+      </c>
+      <c r="BG230" t="inlineStr">
+        <is>
+          <t>1error</t>
+        </is>
+      </c>
+      <c r="BH230" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="231">
       <c r="A231" t="inlineStr">
@@ -63010,6 +68754,31 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BD231" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BE231" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BF231" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BG231" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BH231" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="232">
       <c r="A232" t="inlineStr">
@@ -63281,6 +69050,31 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BD232" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BE232" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BF232" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BG232" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BH232" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="233">
       <c r="A233" t="inlineStr">
@@ -63552,6 +69346,31 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BD233" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BE233" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BF233" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BG233" t="inlineStr">
+        <is>
+          <t>1error</t>
+        </is>
+      </c>
+      <c r="BH233" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="234">
       <c r="A234" t="inlineStr">
@@ -63823,6 +69642,31 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BD234" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BE234" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BF234" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BG234" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BH234" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="235">
       <c r="A235" t="inlineStr">
@@ -64094,6 +69938,31 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BD235" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BE235" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BF235" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BG235" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BH235" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="236">
       <c r="A236" t="inlineStr">
@@ -64365,6 +70234,31 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BD236" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BE236" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BF236" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BG236" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BH236" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="237">
       <c r="A237" t="inlineStr">
@@ -64636,6 +70530,31 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BD237" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BE237" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BF237" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BG237" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BH237" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="238">
       <c r="A238" t="inlineStr">
@@ -64907,6 +70826,31 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BD238" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BE238" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BF238" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BG238" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BH238" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="239">
       <c r="A239" t="inlineStr">
@@ -65178,6 +71122,31 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BD239" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BE239" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BF239" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BG239" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BH239" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="240">
       <c r="A240" t="inlineStr">
@@ -65449,6 +71418,31 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BD240" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BE240" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BF240" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BG240" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BH240" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="241">
       <c r="A241" t="inlineStr">
@@ -65720,6 +71714,31 @@
           <t>1error</t>
         </is>
       </c>
+      <c r="BD241" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BE241" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BF241" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BG241" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BH241" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="242">
       <c r="A242" t="inlineStr">
@@ -65991,6 +72010,31 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BD242" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BE242" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BF242" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BG242" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BH242" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="243">
       <c r="A243" t="inlineStr">
@@ -66262,6 +72306,31 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BD243" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BE243" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BF243" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BG243" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BH243" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="244">
       <c r="A244" t="inlineStr">
@@ -66529,6 +72598,31 @@
         </is>
       </c>
       <c r="BC244" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BD244" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BE244" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BF244" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BG244" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BH244" t="inlineStr">
         <is>
           <t>online</t>
         </is>
@@ -66768,6 +72862,31 @@
         </is>
       </c>
       <c r="BC245" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BD245" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BE245" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BF245" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BG245" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BH245" t="inlineStr">
         <is>
           <t>online</t>
         </is>
@@ -66979,6 +73098,31 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BD246" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BE246" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BF246" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BG246" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BH246" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="247">
       <c r="A247" t="inlineStr">
@@ -67184,6 +73328,31 @@
       <c r="BC247" t="inlineStr">
         <is>
           <t>1error</t>
+        </is>
+      </c>
+      <c r="BD247" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BE247" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BF247" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BG247" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BH247" t="inlineStr">
+        <is>
+          <t>online</t>
         </is>
       </c>
     </row>
@@ -67361,6 +73530,31 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BD248" t="inlineStr">
+        <is>
+          <t>1error</t>
+        </is>
+      </c>
+      <c r="BE248" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BF248" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BG248" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BH248" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="249">
       <c r="A249" t="inlineStr">
@@ -67532,6 +73726,31 @@
         </is>
       </c>
       <c r="BC249" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BD249" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BE249" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BF249" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BG249" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BH249" t="inlineStr">
         <is>
           <t>online</t>
         </is>
@@ -67707,6 +73926,31 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BD250" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BE250" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BF250" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BG250" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BH250" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="251">
       <c r="A251" t="inlineStr">
@@ -67878,6 +74122,31 @@
           <t>2error</t>
         </is>
       </c>
+      <c r="BD251" t="inlineStr">
+        <is>
+          <t>2error</t>
+        </is>
+      </c>
+      <c r="BE251" t="inlineStr">
+        <is>
+          <t>2error</t>
+        </is>
+      </c>
+      <c r="BF251" t="inlineStr">
+        <is>
+          <t>2error</t>
+        </is>
+      </c>
+      <c r="BG251" t="inlineStr">
+        <is>
+          <t>3error</t>
+        </is>
+      </c>
+      <c r="BH251" t="inlineStr">
+        <is>
+          <t>2error</t>
+        </is>
+      </c>
     </row>
     <row r="252">
       <c r="A252" t="inlineStr">
@@ -68049,6 +74318,31 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BD252" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BE252" t="inlineStr">
+        <is>
+          <t>1error</t>
+        </is>
+      </c>
+      <c r="BF252" t="inlineStr">
+        <is>
+          <t>2error</t>
+        </is>
+      </c>
+      <c r="BG252" t="inlineStr">
+        <is>
+          <t>1error</t>
+        </is>
+      </c>
+      <c r="BH252" t="inlineStr">
+        <is>
+          <t>1error</t>
+        </is>
+      </c>
     </row>
     <row r="253">
       <c r="A253" t="inlineStr">
@@ -68218,6 +74512,31 @@
       <c r="BC253" t="inlineStr">
         <is>
           <t>1error</t>
+        </is>
+      </c>
+      <c r="BD253" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BE253" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BF253" t="inlineStr">
+        <is>
+          <t>1error</t>
+        </is>
+      </c>
+      <c r="BG253" t="inlineStr">
+        <is>
+          <t>1error</t>
+        </is>
+      </c>
+      <c r="BH253" t="inlineStr">
+        <is>
+          <t>online</t>
         </is>
       </c>
     </row>
@@ -68311,6 +74630,31 @@
           <t>2error</t>
         </is>
       </c>
+      <c r="BD254" t="inlineStr">
+        <is>
+          <t>2error</t>
+        </is>
+      </c>
+      <c r="BE254" t="inlineStr">
+        <is>
+          <t>2error</t>
+        </is>
+      </c>
+      <c r="BF254" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BG254" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BH254" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="255">
       <c r="A255" t="inlineStr">
@@ -68402,6 +74746,31 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BD255" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BE255" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BF255" t="inlineStr">
+        <is>
+          <t>1error</t>
+        </is>
+      </c>
+      <c r="BG255" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BH255" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="256">
       <c r="A256" t="inlineStr">
@@ -68493,6 +74862,31 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BD256" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BE256" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BF256" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BG256" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BH256" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="257">
       <c r="A257" t="inlineStr">
@@ -68584,6 +74978,31 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BD257" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BE257" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BF257" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BG257" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BH257" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="258">
       <c r="A258" t="inlineStr">
@@ -68675,6 +75094,31 @@
           <t>1error</t>
         </is>
       </c>
+      <c r="BD258" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BE258" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BF258" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BG258" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BH258" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="259">
       <c r="A259" t="inlineStr">
@@ -68766,6 +75210,31 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BD259" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BE259" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BF259" t="inlineStr">
+        <is>
+          <t>2error</t>
+        </is>
+      </c>
+      <c r="BG259" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BH259" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/UATtracking.xlsx
+++ b/UATtracking.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BH259"/>
+  <dimension ref="A1:BI259"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -729,6 +729,11 @@
           <t>0120</t>
         </is>
       </c>
+      <c r="BI1" s="1" t="inlineStr">
+        <is>
+          <t>0121</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -1025,6 +1030,11 @@
           <t>2error</t>
         </is>
       </c>
+      <c r="BI2" t="inlineStr">
+        <is>
+          <t>2error</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -1321,6 +1331,11 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BI3" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -1617,6 +1632,11 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BI4" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -1913,6 +1933,11 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BI5" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -2209,6 +2234,11 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BI6" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -2505,6 +2535,11 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BI7" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -2801,6 +2836,11 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BI8" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -3097,6 +3137,11 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BI9" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -3393,6 +3438,11 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BI10" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -3689,6 +3739,11 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BI11" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -3985,6 +4040,11 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BI12" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -4281,6 +4341,11 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BI13" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -4577,6 +4642,11 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BI14" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -4873,6 +4943,11 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BI15" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -5169,6 +5244,11 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BI16" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -5465,6 +5545,11 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BI17" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -5761,6 +5846,11 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BI18" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -6057,6 +6147,11 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BI19" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -6353,6 +6448,11 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BI20" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -6649,6 +6749,11 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BI21" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -6945,6 +7050,11 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BI22" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -7241,6 +7351,11 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BI23" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -7537,6 +7652,11 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BI24" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -7833,6 +7953,11 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BI25" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -8129,6 +8254,11 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BI26" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -8425,6 +8555,11 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BI27" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -8721,6 +8856,11 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BI28" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -9017,6 +9157,11 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BI29" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -9313,6 +9458,11 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BI30" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -9609,6 +9759,11 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BI31" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -9905,6 +10060,11 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BI32" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -10201,6 +10361,11 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BI33" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -10497,6 +10662,11 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BI34" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -10791,6 +10961,11 @@
           <t>offline</t>
         </is>
       </c>
+      <c r="BI35" t="inlineStr">
+        <is>
+          <t>offline</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -11087,6 +11262,11 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BI36" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -11383,6 +11563,11 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BI37" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -11679,6 +11864,11 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BI38" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -11975,6 +12165,11 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BI39" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -12271,6 +12466,11 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BI40" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -12567,6 +12767,11 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BI41" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -12863,6 +13068,11 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BI42" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -13159,6 +13369,11 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BI43" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -13455,6 +13670,11 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BI44" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -13751,6 +13971,11 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BI45" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -14047,6 +14272,11 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BI46" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -14343,6 +14573,11 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BI47" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -14639,6 +14874,11 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BI48" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -14935,6 +15175,11 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BI49" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -15231,6 +15476,11 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BI50" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -15527,6 +15777,11 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BI51" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -15823,6 +16078,11 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BI52" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -16117,6 +16377,11 @@
           <t>offline</t>
         </is>
       </c>
+      <c r="BI53" t="inlineStr">
+        <is>
+          <t>offline</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -16411,6 +16676,11 @@
           <t>offline</t>
         </is>
       </c>
+      <c r="BI54" t="inlineStr">
+        <is>
+          <t>offline</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -16707,6 +16977,11 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BI55" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -17003,6 +17278,11 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BI56" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -17299,6 +17579,11 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BI57" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -17595,6 +17880,11 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BI58" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -17891,6 +18181,11 @@
           <t>1error</t>
         </is>
       </c>
+      <c r="BI59" t="inlineStr">
+        <is>
+          <t>1error</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -18187,6 +18482,11 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BI60" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -18483,6 +18783,11 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BI61" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -18779,6 +19084,11 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BI62" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -19075,6 +19385,11 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BI63" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -19371,6 +19686,11 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BI64" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -19667,6 +19987,11 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BI65" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -19963,6 +20288,11 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BI66" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -20259,6 +20589,11 @@
           <t>1error</t>
         </is>
       </c>
+      <c r="BI67" t="inlineStr">
+        <is>
+          <t>1error</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -20555,6 +20890,11 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BI68" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -20851,6 +21191,11 @@
           <t>2error</t>
         </is>
       </c>
+      <c r="BI69" t="inlineStr">
+        <is>
+          <t>2error</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -21147,6 +21492,11 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BI70" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -21443,6 +21793,11 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BI71" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -21739,6 +22094,11 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BI72" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -22035,6 +22395,11 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BI73" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -22331,6 +22696,11 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BI74" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -22627,6 +22997,11 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BI75" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -22923,6 +23298,11 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BI76" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
@@ -23219,6 +23599,11 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BI77" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
@@ -23515,6 +23900,11 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BI78" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
@@ -23811,6 +24201,11 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BI79" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
@@ -24105,6 +24500,11 @@
           <t>offline</t>
         </is>
       </c>
+      <c r="BI80" t="inlineStr">
+        <is>
+          <t>offline</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
@@ -24401,6 +24801,11 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BI81" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
@@ -24697,6 +25102,11 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BI82" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
@@ -24993,6 +25403,11 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BI83" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
@@ -25289,6 +25704,11 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BI84" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
@@ -25585,6 +26005,11 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BI85" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
@@ -25881,6 +26306,11 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BI86" t="inlineStr">
+        <is>
+          <t>2error</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
@@ -26177,6 +26607,11 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BI87" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
@@ -26473,6 +26908,11 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BI88" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
@@ -26769,6 +27209,11 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BI89" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
@@ -27065,6 +27510,11 @@
           <t>2error</t>
         </is>
       </c>
+      <c r="BI90" t="inlineStr">
+        <is>
+          <t>2error</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
@@ -27361,6 +27811,11 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BI91" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
@@ -27657,6 +28112,11 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BI92" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
@@ -27953,6 +28413,11 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BI93" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
@@ -28249,6 +28714,11 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BI94" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
@@ -28545,6 +29015,11 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BI95" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
@@ -28841,6 +29316,11 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BI96" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
@@ -29137,6 +29617,11 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BI97" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
@@ -29433,6 +29918,11 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BI98" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
@@ -29727,6 +30217,11 @@
           <t>offline</t>
         </is>
       </c>
+      <c r="BI99" t="inlineStr">
+        <is>
+          <t>offline</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
@@ -30023,6 +30518,11 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BI100" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
@@ -30319,6 +30819,11 @@
           <t>1error</t>
         </is>
       </c>
+      <c r="BI101" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
@@ -30615,6 +31120,11 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BI102" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
@@ -30911,6 +31421,11 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BI103" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
@@ -31207,6 +31722,11 @@
           <t>2error</t>
         </is>
       </c>
+      <c r="BI104" t="inlineStr">
+        <is>
+          <t>2error</t>
+        </is>
+      </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
@@ -31503,6 +32023,11 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BI105" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
@@ -31799,6 +32324,11 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BI106" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
@@ -32095,6 +32625,11 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BI107" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
@@ -32391,6 +32926,11 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BI108" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
@@ -32687,6 +33227,11 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BI109" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
@@ -32983,6 +33528,11 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BI110" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
@@ -33279,6 +33829,11 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BI111" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
@@ -33575,6 +34130,11 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BI112" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
@@ -33871,6 +34431,11 @@
           <t>1error</t>
         </is>
       </c>
+      <c r="BI113" t="inlineStr">
+        <is>
+          <t>1error</t>
+        </is>
+      </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
@@ -34167,6 +34732,11 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BI114" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
@@ -34463,6 +35033,11 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BI115" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
@@ -34759,6 +35334,11 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BI116" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
@@ -35053,6 +35633,11 @@
           <t>offline</t>
         </is>
       </c>
+      <c r="BI117" t="inlineStr">
+        <is>
+          <t>offline</t>
+        </is>
+      </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
@@ -35349,6 +35934,11 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BI118" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
@@ -35643,6 +36233,11 @@
           <t>offline</t>
         </is>
       </c>
+      <c r="BI119" t="inlineStr">
+        <is>
+          <t>offline</t>
+        </is>
+      </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
@@ -35939,6 +36534,11 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BI120" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
@@ -36235,6 +36835,11 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BI121" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
@@ -36531,6 +37136,11 @@
           <t>1error</t>
         </is>
       </c>
+      <c r="BI122" t="inlineStr">
+        <is>
+          <t>1error</t>
+        </is>
+      </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
@@ -36827,6 +37437,11 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BI123" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
@@ -37123,6 +37738,11 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BI124" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
@@ -37419,6 +38039,11 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BI125" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
@@ -37713,6 +38338,11 @@
           <t>offline</t>
         </is>
       </c>
+      <c r="BI126" t="inlineStr">
+        <is>
+          <t>offline</t>
+        </is>
+      </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
@@ -38009,6 +38639,11 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BI127" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
@@ -38305,6 +38940,11 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BI128" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
@@ -38601,6 +39241,11 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BI129" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
@@ -38897,6 +39542,11 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BI130" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
@@ -39193,6 +39843,11 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BI131" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
@@ -39489,6 +40144,11 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BI132" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
@@ -39783,6 +40443,11 @@
           <t>offline</t>
         </is>
       </c>
+      <c r="BI133" t="inlineStr">
+        <is>
+          <t>offline</t>
+        </is>
+      </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
@@ -40079,6 +40744,11 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BI134" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
@@ -40375,6 +41045,11 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BI135" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
@@ -40671,6 +41346,11 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BI136" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
@@ -40967,6 +41647,11 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BI137" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
@@ -41261,6 +41946,11 @@
           <t>offline</t>
         </is>
       </c>
+      <c r="BI138" t="inlineStr">
+        <is>
+          <t>offline</t>
+        </is>
+      </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
@@ -41557,6 +42247,11 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BI139" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
@@ -41853,6 +42548,11 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BI140" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
@@ -42149,6 +42849,11 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BI141" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
@@ -42445,6 +43150,11 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BI142" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
@@ -42741,6 +43451,11 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BI143" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
@@ -43037,6 +43752,11 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BI144" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
@@ -43333,6 +44053,11 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BI145" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
@@ -43629,6 +44354,11 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BI146" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
@@ -43925,6 +44655,11 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BI147" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
@@ -44221,6 +44956,11 @@
           <t>1error</t>
         </is>
       </c>
+      <c r="BI148" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
@@ -44517,6 +45257,11 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BI149" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
@@ -44813,6 +45558,11 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BI150" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
@@ -45109,6 +45859,11 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BI151" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
@@ -45403,6 +46158,11 @@
           <t>offline</t>
         </is>
       </c>
+      <c r="BI152" t="inlineStr">
+        <is>
+          <t>offline</t>
+        </is>
+      </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
@@ -45699,6 +46459,11 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BI153" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
@@ -45995,6 +46760,11 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BI154" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
@@ -46291,6 +47061,11 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BI155" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
@@ -46587,6 +47362,11 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BI156" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
@@ -46883,6 +47663,11 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BI157" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
@@ -47179,6 +47964,11 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BI158" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
@@ -47475,6 +48265,11 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BI159" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
@@ -47771,6 +48566,11 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BI160" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
@@ -48067,6 +48867,11 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BI161" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
@@ -48363,6 +49168,11 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BI162" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
@@ -48659,6 +49469,11 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BI163" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
@@ -48955,6 +49770,11 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BI164" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
@@ -49251,6 +50071,11 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BI165" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
@@ -49547,6 +50372,11 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BI166" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
@@ -49843,6 +50673,11 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BI167" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
@@ -50137,6 +50972,11 @@
           <t>offline</t>
         </is>
       </c>
+      <c r="BI168" t="inlineStr">
+        <is>
+          <t>offline</t>
+        </is>
+      </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
@@ -50433,6 +51273,11 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BI169" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
@@ -50729,6 +51574,11 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BI170" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
@@ -51025,6 +51875,11 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BI171" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
@@ -51321,6 +52176,11 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BI172" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
@@ -51617,6 +52477,11 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BI173" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
@@ -51913,6 +52778,11 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BI174" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
@@ -52209,6 +53079,11 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BI175" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
@@ -52505,6 +53380,11 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BI176" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
@@ -52799,6 +53679,11 @@
           <t>offline</t>
         </is>
       </c>
+      <c r="BI177" t="inlineStr">
+        <is>
+          <t>offline</t>
+        </is>
+      </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
@@ -53095,6 +53980,11 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BI178" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
@@ -53391,6 +54281,11 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BI179" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
@@ -53687,6 +54582,11 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BI180" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
@@ -53983,6 +54883,11 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BI181" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
@@ -54277,6 +55182,11 @@
           <t>offline</t>
         </is>
       </c>
+      <c r="BI182" t="inlineStr">
+        <is>
+          <t>offline</t>
+        </is>
+      </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
@@ -54573,6 +55483,11 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BI183" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
@@ -54869,6 +55784,11 @@
           <t>1error</t>
         </is>
       </c>
+      <c r="BI184" t="inlineStr">
+        <is>
+          <t>1error</t>
+        </is>
+      </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
@@ -55165,6 +56085,11 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BI185" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
@@ -55461,6 +56386,11 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BI186" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
@@ -55757,6 +56687,11 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BI187" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
@@ -56051,6 +56986,11 @@
           <t>offline</t>
         </is>
       </c>
+      <c r="BI188" t="inlineStr">
+        <is>
+          <t>offline</t>
+        </is>
+      </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
@@ -56347,6 +57287,11 @@
           <t>1error</t>
         </is>
       </c>
+      <c r="BI189" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
@@ -56643,6 +57588,11 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BI190" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
@@ -56939,6 +57889,11 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BI191" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
@@ -57235,6 +58190,11 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BI192" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
@@ -57531,6 +58491,11 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BI193" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
@@ -57827,6 +58792,11 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BI194" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
@@ -58123,6 +59093,11 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BI195" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
@@ -58419,6 +59394,11 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BI196" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
@@ -58715,6 +59695,11 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BI197" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
@@ -59011,6 +59996,11 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BI198" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
@@ -59307,6 +60297,11 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BI199" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
@@ -59603,6 +60598,11 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BI200" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
@@ -59899,6 +60899,11 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BI201" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
@@ -60195,6 +61200,11 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BI202" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
@@ -60491,6 +61501,11 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BI203" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
@@ -60787,6 +61802,11 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BI204" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
@@ -61083,6 +62103,11 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BI205" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
@@ -61379,6 +62404,11 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BI206" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
@@ -61675,6 +62705,11 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BI207" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
@@ -61971,6 +63006,11 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BI208" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
@@ -62267,6 +63307,11 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BI209" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
@@ -62563,6 +63608,11 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BI210" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
@@ -62859,6 +63909,11 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BI211" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
@@ -63155,6 +64210,11 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BI212" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
@@ -63451,6 +64511,11 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BI213" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
@@ -63747,6 +64812,11 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BI214" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
@@ -64043,6 +65113,11 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BI215" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
@@ -64339,6 +65414,11 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BI216" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
@@ -64635,6 +65715,11 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BI217" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
@@ -64931,6 +66016,11 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BI218" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
@@ -65227,6 +66317,11 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BI219" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
@@ -65523,6 +66618,11 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BI220" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="221">
       <c r="A221" t="inlineStr">
@@ -65819,6 +66919,11 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BI221" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="222">
       <c r="A222" t="inlineStr">
@@ -66115,6 +67220,11 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BI222" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr">
@@ -66411,6 +67521,11 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BI223" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="224">
       <c r="A224" t="inlineStr">
@@ -66707,6 +67822,11 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BI224" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="225">
       <c r="A225" t="inlineStr">
@@ -67003,6 +68123,11 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BI225" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="226">
       <c r="A226" t="inlineStr">
@@ -67299,6 +68424,11 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BI226" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="227">
       <c r="A227" t="inlineStr">
@@ -67595,6 +68725,11 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BI227" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="228">
       <c r="A228" t="inlineStr">
@@ -67891,6 +69026,11 @@
           <t>1error</t>
         </is>
       </c>
+      <c r="BI228" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="229">
       <c r="A229" t="inlineStr">
@@ -68187,6 +69327,11 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BI229" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="230">
       <c r="A230" t="inlineStr">
@@ -68483,6 +69628,11 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BI230" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="231">
       <c r="A231" t="inlineStr">
@@ -68779,6 +69929,11 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BI231" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="232">
       <c r="A232" t="inlineStr">
@@ -69075,6 +70230,11 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BI232" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="233">
       <c r="A233" t="inlineStr">
@@ -69371,6 +70531,11 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BI233" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="234">
       <c r="A234" t="inlineStr">
@@ -69667,6 +70832,11 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BI234" t="inlineStr">
+        <is>
+          <t>1error</t>
+        </is>
+      </c>
     </row>
     <row r="235">
       <c r="A235" t="inlineStr">
@@ -69963,6 +71133,11 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BI235" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="236">
       <c r="A236" t="inlineStr">
@@ -70259,6 +71434,11 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BI236" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="237">
       <c r="A237" t="inlineStr">
@@ -70555,6 +71735,11 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BI237" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="238">
       <c r="A238" t="inlineStr">
@@ -70851,6 +72036,11 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BI238" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="239">
       <c r="A239" t="inlineStr">
@@ -71147,6 +72337,11 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BI239" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="240">
       <c r="A240" t="inlineStr">
@@ -71443,6 +72638,11 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BI240" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="241">
       <c r="A241" t="inlineStr">
@@ -71739,6 +72939,11 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BI241" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="242">
       <c r="A242" t="inlineStr">
@@ -72035,6 +73240,11 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BI242" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="243">
       <c r="A243" t="inlineStr">
@@ -72331,6 +73541,11 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BI243" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="244">
       <c r="A244" t="inlineStr">
@@ -72623,6 +73838,11 @@
         </is>
       </c>
       <c r="BH244" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BI244" t="inlineStr">
         <is>
           <t>online</t>
         </is>
@@ -72887,6 +74107,11 @@
         </is>
       </c>
       <c r="BH245" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BI245" t="inlineStr">
         <is>
           <t>online</t>
         </is>
@@ -73123,6 +74348,11 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BI246" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="247">
       <c r="A247" t="inlineStr">
@@ -73351,6 +74581,11 @@
         </is>
       </c>
       <c r="BH247" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BI247" t="inlineStr">
         <is>
           <t>online</t>
         </is>
@@ -73555,6 +74790,11 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BI248" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="249">
       <c r="A249" t="inlineStr">
@@ -73751,6 +74991,11 @@
         </is>
       </c>
       <c r="BH249" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BI249" t="inlineStr">
         <is>
           <t>online</t>
         </is>
@@ -73951,6 +75196,11 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BI250" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="251">
       <c r="A251" t="inlineStr">
@@ -74147,6 +75397,11 @@
           <t>2error</t>
         </is>
       </c>
+      <c r="BI251" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="252">
       <c r="A252" t="inlineStr">
@@ -74343,6 +75598,11 @@
           <t>1error</t>
         </is>
       </c>
+      <c r="BI252" t="inlineStr">
+        <is>
+          <t>1error</t>
+        </is>
+      </c>
     </row>
     <row r="253">
       <c r="A253" t="inlineStr">
@@ -74535,6 +75795,11 @@
         </is>
       </c>
       <c r="BH253" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BI253" t="inlineStr">
         <is>
           <t>online</t>
         </is>
@@ -74655,6 +75920,11 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BI254" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="255">
       <c r="A255" t="inlineStr">
@@ -74771,6 +76041,11 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BI255" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="256">
       <c r="A256" t="inlineStr">
@@ -74887,6 +76162,11 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BI256" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="257">
       <c r="A257" t="inlineStr">
@@ -75003,6 +76283,11 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BI257" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="258">
       <c r="A258" t="inlineStr">
@@ -75119,6 +76404,11 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BI258" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="259">
       <c r="A259" t="inlineStr">
@@ -75235,6 +76525,11 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BI259" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/UATtracking.xlsx
+++ b/UATtracking.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BI259"/>
+  <dimension ref="A1:BJ259"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -734,6 +734,11 @@
           <t>0121</t>
         </is>
       </c>
+      <c r="BJ1" s="1" t="inlineStr">
+        <is>
+          <t>0122</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -1035,6 +1040,11 @@
           <t>2error</t>
         </is>
       </c>
+      <c r="BJ2" t="inlineStr">
+        <is>
+          <t>2error</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -1336,6 +1346,11 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BJ3" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -1637,6 +1652,11 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BJ4" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -1938,6 +1958,11 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BJ5" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -2239,6 +2264,11 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BJ6" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -2540,6 +2570,11 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BJ7" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -2841,6 +2876,11 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BJ8" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -3142,6 +3182,11 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BJ9" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -3443,6 +3488,11 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BJ10" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -3744,6 +3794,11 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BJ11" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -4045,6 +4100,11 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BJ12" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -4346,6 +4406,11 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BJ13" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -4647,6 +4712,11 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BJ14" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -4948,6 +5018,11 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BJ15" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -5249,6 +5324,11 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BJ16" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -5550,6 +5630,11 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BJ17" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -5851,6 +5936,11 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BJ18" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -6152,6 +6242,11 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BJ19" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -6453,6 +6548,11 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BJ20" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -6754,6 +6854,11 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BJ21" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -7055,6 +7160,11 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BJ22" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -7356,6 +7466,11 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BJ23" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -7657,6 +7772,11 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BJ24" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -7958,6 +8078,11 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BJ25" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -8259,6 +8384,11 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BJ26" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -8560,6 +8690,11 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BJ27" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -8861,6 +8996,11 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BJ28" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -9162,6 +9302,11 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BJ29" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -9463,6 +9608,11 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BJ30" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -9764,6 +9914,11 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BJ31" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -10065,6 +10220,11 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BJ32" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -10366,6 +10526,11 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BJ33" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -10667,6 +10832,11 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BJ34" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -10966,6 +11136,11 @@
           <t>offline</t>
         </is>
       </c>
+      <c r="BJ35" t="inlineStr">
+        <is>
+          <t>offline</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -11267,6 +11442,11 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BJ36" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -11568,6 +11748,11 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BJ37" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -11869,6 +12054,11 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BJ38" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -12170,6 +12360,11 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BJ39" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -12471,6 +12666,11 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BJ40" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -12772,6 +12972,11 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BJ41" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -13073,6 +13278,11 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BJ42" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -13374,6 +13584,11 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BJ43" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -13675,6 +13890,11 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BJ44" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -13976,6 +14196,11 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BJ45" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -14277,6 +14502,11 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BJ46" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -14578,6 +14808,11 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BJ47" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -14879,6 +15114,11 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BJ48" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -15180,6 +15420,11 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BJ49" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -15481,6 +15726,11 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BJ50" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -15782,6 +16032,11 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BJ51" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -16083,6 +16338,11 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BJ52" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -16382,6 +16642,11 @@
           <t>offline</t>
         </is>
       </c>
+      <c r="BJ53" t="inlineStr">
+        <is>
+          <t>offline</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -16681,6 +16946,11 @@
           <t>offline</t>
         </is>
       </c>
+      <c r="BJ54" t="inlineStr">
+        <is>
+          <t>offline</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -16982,6 +17252,11 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BJ55" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -17283,6 +17558,11 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BJ56" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -17584,6 +17864,11 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BJ57" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -17885,6 +18170,11 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BJ58" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -18186,6 +18476,11 @@
           <t>1error</t>
         </is>
       </c>
+      <c r="BJ59" t="inlineStr">
+        <is>
+          <t>1error</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -18487,6 +18782,11 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BJ60" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -18788,6 +19088,11 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BJ61" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -19089,6 +19394,11 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BJ62" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -19390,6 +19700,11 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BJ63" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -19691,6 +20006,11 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BJ64" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -19992,6 +20312,11 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BJ65" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -20293,6 +20618,11 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BJ66" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -20594,6 +20924,11 @@
           <t>1error</t>
         </is>
       </c>
+      <c r="BJ67" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -20895,6 +21230,11 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BJ68" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -21196,6 +21536,11 @@
           <t>2error</t>
         </is>
       </c>
+      <c r="BJ69" t="inlineStr">
+        <is>
+          <t>2error</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -21497,6 +21842,11 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BJ70" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -21798,6 +22148,11 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BJ71" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -22099,6 +22454,11 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BJ72" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -22400,6 +22760,11 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BJ73" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -22701,6 +23066,11 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BJ74" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -23002,6 +23372,11 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BJ75" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -23303,6 +23678,11 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BJ76" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
@@ -23604,6 +23984,11 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BJ77" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
@@ -23905,6 +24290,11 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BJ78" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
@@ -24206,6 +24596,11 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BJ79" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
@@ -24505,6 +24900,11 @@
           <t>offline</t>
         </is>
       </c>
+      <c r="BJ80" t="inlineStr">
+        <is>
+          <t>offline</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
@@ -24806,6 +25206,11 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BJ81" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
@@ -25107,6 +25512,11 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BJ82" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
@@ -25408,6 +25818,11 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BJ83" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
@@ -25709,6 +26124,11 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BJ84" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
@@ -26010,6 +26430,11 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BJ85" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
@@ -26311,6 +26736,11 @@
           <t>2error</t>
         </is>
       </c>
+      <c r="BJ86" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
@@ -26612,6 +27042,11 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BJ87" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
@@ -26913,6 +27348,11 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BJ88" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
@@ -27214,6 +27654,11 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BJ89" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
@@ -27515,6 +27960,11 @@
           <t>2error</t>
         </is>
       </c>
+      <c r="BJ90" t="inlineStr">
+        <is>
+          <t>2error</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
@@ -27816,6 +28266,11 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BJ91" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
@@ -28117,6 +28572,11 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BJ92" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
@@ -28418,6 +28878,11 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BJ93" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
@@ -28719,6 +29184,11 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BJ94" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
@@ -29020,6 +29490,11 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BJ95" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
@@ -29321,6 +29796,11 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BJ96" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
@@ -29622,6 +30102,11 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BJ97" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
@@ -29923,6 +30408,11 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BJ98" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
@@ -30222,6 +30712,11 @@
           <t>offline</t>
         </is>
       </c>
+      <c r="BJ99" t="inlineStr">
+        <is>
+          <t>offline</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
@@ -30523,6 +31018,11 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BJ100" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
@@ -30824,6 +31324,11 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BJ101" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
@@ -31125,6 +31630,11 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BJ102" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
@@ -31426,6 +31936,11 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BJ103" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
@@ -31727,6 +32242,11 @@
           <t>2error</t>
         </is>
       </c>
+      <c r="BJ104" t="inlineStr">
+        <is>
+          <t>2error</t>
+        </is>
+      </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
@@ -32028,6 +32548,11 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BJ105" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
@@ -32329,6 +32854,11 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BJ106" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
@@ -32630,6 +33160,11 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BJ107" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
@@ -32931,6 +33466,11 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BJ108" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
@@ -33232,6 +33772,11 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BJ109" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
@@ -33533,6 +34078,11 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BJ110" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
@@ -33834,6 +34384,11 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BJ111" t="inlineStr">
+        <is>
+          <t>1error</t>
+        </is>
+      </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
@@ -34135,6 +34690,11 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BJ112" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
@@ -34436,6 +34996,11 @@
           <t>1error</t>
         </is>
       </c>
+      <c r="BJ113" t="inlineStr">
+        <is>
+          <t>1error</t>
+        </is>
+      </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
@@ -34737,6 +35302,11 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BJ114" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
@@ -35038,6 +35608,11 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BJ115" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
@@ -35339,6 +35914,11 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BJ116" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
@@ -35638,6 +36218,11 @@
           <t>offline</t>
         </is>
       </c>
+      <c r="BJ117" t="inlineStr">
+        <is>
+          <t>offline</t>
+        </is>
+      </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
@@ -35939,6 +36524,11 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BJ118" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
@@ -36238,6 +36828,11 @@
           <t>offline</t>
         </is>
       </c>
+      <c r="BJ119" t="inlineStr">
+        <is>
+          <t>offline</t>
+        </is>
+      </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
@@ -36539,6 +37134,11 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BJ120" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
@@ -36840,6 +37440,11 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BJ121" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
@@ -37141,6 +37746,11 @@
           <t>1error</t>
         </is>
       </c>
+      <c r="BJ122" t="inlineStr">
+        <is>
+          <t>1error</t>
+        </is>
+      </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
@@ -37442,6 +38052,11 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BJ123" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
@@ -37743,6 +38358,11 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BJ124" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
@@ -38044,6 +38664,11 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BJ125" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
@@ -38343,6 +38968,11 @@
           <t>offline</t>
         </is>
       </c>
+      <c r="BJ126" t="inlineStr">
+        <is>
+          <t>offline</t>
+        </is>
+      </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
@@ -38644,6 +39274,11 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BJ127" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
@@ -38945,6 +39580,11 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BJ128" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
@@ -39246,6 +39886,11 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BJ129" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
@@ -39547,6 +40192,11 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BJ130" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
@@ -39848,6 +40498,11 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BJ131" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
@@ -40149,6 +40804,11 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BJ132" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
@@ -40448,6 +41108,11 @@
           <t>offline</t>
         </is>
       </c>
+      <c r="BJ133" t="inlineStr">
+        <is>
+          <t>offline</t>
+        </is>
+      </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
@@ -40749,6 +41414,11 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BJ134" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
@@ -41050,6 +41720,11 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BJ135" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
@@ -41351,6 +42026,11 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BJ136" t="inlineStr">
+        <is>
+          <t>1error</t>
+        </is>
+      </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
@@ -41652,6 +42332,11 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BJ137" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
@@ -41951,6 +42636,11 @@
           <t>offline</t>
         </is>
       </c>
+      <c r="BJ138" t="inlineStr">
+        <is>
+          <t>offline</t>
+        </is>
+      </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
@@ -42252,6 +42942,11 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BJ139" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
@@ -42553,6 +43248,11 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BJ140" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
@@ -42854,6 +43554,11 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BJ141" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
@@ -43155,6 +43860,11 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BJ142" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
@@ -43456,6 +44166,11 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BJ143" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
@@ -43757,6 +44472,11 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BJ144" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
@@ -44058,6 +44778,11 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BJ145" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
@@ -44359,6 +45084,11 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BJ146" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
@@ -44660,6 +45390,11 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BJ147" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
@@ -44961,6 +45696,11 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BJ148" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
@@ -45262,6 +46002,11 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BJ149" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
@@ -45563,6 +46308,11 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BJ150" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
@@ -45864,6 +46614,11 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BJ151" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
@@ -46163,6 +46918,11 @@
           <t>offline</t>
         </is>
       </c>
+      <c r="BJ152" t="inlineStr">
+        <is>
+          <t>offline</t>
+        </is>
+      </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
@@ -46464,6 +47224,11 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BJ153" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
@@ -46765,6 +47530,11 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BJ154" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
@@ -47066,6 +47836,11 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BJ155" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
@@ -47367,6 +48142,11 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BJ156" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
@@ -47668,6 +48448,11 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BJ157" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
@@ -47969,6 +48754,11 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BJ158" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
@@ -48270,6 +49060,11 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BJ159" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
@@ -48571,6 +49366,11 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BJ160" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
@@ -48872,6 +49672,11 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BJ161" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
@@ -49173,6 +49978,11 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BJ162" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
@@ -49474,6 +50284,11 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BJ163" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
@@ -49775,6 +50590,11 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BJ164" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
@@ -50076,6 +50896,11 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BJ165" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
@@ -50377,6 +51202,11 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BJ166" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
@@ -50678,6 +51508,11 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BJ167" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
@@ -50977,6 +51812,11 @@
           <t>offline</t>
         </is>
       </c>
+      <c r="BJ168" t="inlineStr">
+        <is>
+          <t>offline</t>
+        </is>
+      </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
@@ -51278,6 +52118,11 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BJ169" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
@@ -51579,6 +52424,11 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BJ170" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
@@ -51880,6 +52730,11 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BJ171" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
@@ -52181,6 +53036,11 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BJ172" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
@@ -52482,6 +53342,11 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BJ173" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
@@ -52783,6 +53648,11 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BJ174" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
@@ -53084,6 +53954,11 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BJ175" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
@@ -53385,6 +54260,11 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BJ176" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
@@ -53684,6 +54564,11 @@
           <t>offline</t>
         </is>
       </c>
+      <c r="BJ177" t="inlineStr">
+        <is>
+          <t>offline</t>
+        </is>
+      </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
@@ -53985,6 +54870,11 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BJ178" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
@@ -54286,6 +55176,11 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BJ179" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
@@ -54587,6 +55482,11 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BJ180" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
@@ -54888,6 +55788,11 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BJ181" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
@@ -55187,6 +56092,11 @@
           <t>offline</t>
         </is>
       </c>
+      <c r="BJ182" t="inlineStr">
+        <is>
+          <t>offline</t>
+        </is>
+      </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
@@ -55488,6 +56398,11 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BJ183" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
@@ -55789,6 +56704,11 @@
           <t>1error</t>
         </is>
       </c>
+      <c r="BJ184" t="inlineStr">
+        <is>
+          <t>1error</t>
+        </is>
+      </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
@@ -56090,6 +57010,11 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BJ185" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
@@ -56391,6 +57316,11 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BJ186" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
@@ -56692,6 +57622,11 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BJ187" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
@@ -56991,6 +57926,11 @@
           <t>offline</t>
         </is>
       </c>
+      <c r="BJ188" t="inlineStr">
+        <is>
+          <t>offline</t>
+        </is>
+      </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
@@ -57292,6 +58232,11 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BJ189" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
@@ -57593,6 +58538,11 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BJ190" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
@@ -57894,6 +58844,11 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BJ191" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
@@ -58195,6 +59150,11 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BJ192" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
@@ -58496,6 +59456,11 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BJ193" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
@@ -58797,6 +59762,11 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BJ194" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
@@ -59098,6 +60068,11 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BJ195" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
@@ -59399,6 +60374,11 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BJ196" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
@@ -59700,6 +60680,11 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BJ197" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
@@ -60001,6 +60986,11 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BJ198" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
@@ -60302,6 +61292,11 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BJ199" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
@@ -60603,6 +61598,11 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BJ200" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
@@ -60904,6 +61904,11 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BJ201" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
@@ -61205,6 +62210,11 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BJ202" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
@@ -61506,6 +62516,11 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BJ203" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
@@ -61807,6 +62822,11 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BJ204" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
@@ -62108,6 +63128,11 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BJ205" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
@@ -62409,6 +63434,11 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BJ206" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
@@ -62710,6 +63740,11 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BJ207" t="inlineStr">
+        <is>
+          <t>1error</t>
+        </is>
+      </c>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
@@ -63011,6 +64046,11 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BJ208" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
@@ -63312,6 +64352,11 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BJ209" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
@@ -63613,6 +64658,11 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BJ210" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
@@ -63914,6 +64964,11 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BJ211" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
@@ -64215,6 +65270,11 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BJ212" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
@@ -64516,6 +65576,11 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BJ213" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
@@ -64817,6 +65882,11 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BJ214" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
@@ -65118,6 +66188,11 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BJ215" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
@@ -65419,6 +66494,11 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BJ216" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
@@ -65720,6 +66800,11 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BJ217" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
@@ -66021,6 +67106,11 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BJ218" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
@@ -66322,6 +67412,11 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BJ219" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
@@ -66623,6 +67718,11 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BJ220" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="221">
       <c r="A221" t="inlineStr">
@@ -66924,6 +68024,11 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BJ221" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="222">
       <c r="A222" t="inlineStr">
@@ -67225,6 +68330,11 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BJ222" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr">
@@ -67526,6 +68636,11 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BJ223" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="224">
       <c r="A224" t="inlineStr">
@@ -67827,6 +68942,11 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BJ224" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="225">
       <c r="A225" t="inlineStr">
@@ -68128,6 +69248,11 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BJ225" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="226">
       <c r="A226" t="inlineStr">
@@ -68429,6 +69554,11 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BJ226" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="227">
       <c r="A227" t="inlineStr">
@@ -68730,6 +69860,11 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BJ227" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="228">
       <c r="A228" t="inlineStr">
@@ -69031,6 +70166,11 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BJ228" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="229">
       <c r="A229" t="inlineStr">
@@ -69332,6 +70472,11 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BJ229" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="230">
       <c r="A230" t="inlineStr">
@@ -69633,6 +70778,11 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BJ230" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="231">
       <c r="A231" t="inlineStr">
@@ -69934,6 +71084,11 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BJ231" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="232">
       <c r="A232" t="inlineStr">
@@ -70235,6 +71390,11 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BJ232" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="233">
       <c r="A233" t="inlineStr">
@@ -70536,6 +71696,11 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BJ233" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="234">
       <c r="A234" t="inlineStr">
@@ -70837,6 +72002,11 @@
           <t>1error</t>
         </is>
       </c>
+      <c r="BJ234" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="235">
       <c r="A235" t="inlineStr">
@@ -71138,6 +72308,11 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BJ235" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="236">
       <c r="A236" t="inlineStr">
@@ -71439,6 +72614,11 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BJ236" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="237">
       <c r="A237" t="inlineStr">
@@ -71740,6 +72920,11 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BJ237" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="238">
       <c r="A238" t="inlineStr">
@@ -72041,6 +73226,11 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BJ238" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="239">
       <c r="A239" t="inlineStr">
@@ -72342,6 +73532,11 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BJ239" t="inlineStr">
+        <is>
+          <t>1error</t>
+        </is>
+      </c>
     </row>
     <row r="240">
       <c r="A240" t="inlineStr">
@@ -72643,6 +73838,11 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BJ240" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="241">
       <c r="A241" t="inlineStr">
@@ -72944,6 +74144,11 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BJ241" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="242">
       <c r="A242" t="inlineStr">
@@ -73245,6 +74450,11 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BJ242" t="inlineStr">
+        <is>
+          <t>1error</t>
+        </is>
+      </c>
     </row>
     <row r="243">
       <c r="A243" t="inlineStr">
@@ -73546,6 +74756,11 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BJ243" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="244">
       <c r="A244" t="inlineStr">
@@ -73843,6 +75058,11 @@
         </is>
       </c>
       <c r="BI244" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BJ244" t="inlineStr">
         <is>
           <t>online</t>
         </is>
@@ -74112,6 +75332,11 @@
         </is>
       </c>
       <c r="BI245" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BJ245" t="inlineStr">
         <is>
           <t>online</t>
         </is>
@@ -74353,6 +75578,11 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BJ246" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="247">
       <c r="A247" t="inlineStr">
@@ -74586,6 +75816,11 @@
         </is>
       </c>
       <c r="BI247" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BJ247" t="inlineStr">
         <is>
           <t>online</t>
         </is>
@@ -74795,6 +76030,11 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BJ248" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="249">
       <c r="A249" t="inlineStr">
@@ -74996,6 +76236,11 @@
         </is>
       </c>
       <c r="BI249" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BJ249" t="inlineStr">
         <is>
           <t>online</t>
         </is>
@@ -75201,6 +76446,11 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BJ250" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="251">
       <c r="A251" t="inlineStr">
@@ -75402,6 +76652,11 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BJ251" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="252">
       <c r="A252" t="inlineStr">
@@ -75603,6 +76858,11 @@
           <t>1error</t>
         </is>
       </c>
+      <c r="BJ252" t="inlineStr">
+        <is>
+          <t>1error</t>
+        </is>
+      </c>
     </row>
     <row r="253">
       <c r="A253" t="inlineStr">
@@ -75800,6 +77060,11 @@
         </is>
       </c>
       <c r="BI253" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BJ253" t="inlineStr">
         <is>
           <t>online</t>
         </is>
@@ -75925,6 +77190,11 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BJ254" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="255">
       <c r="A255" t="inlineStr">
@@ -76046,6 +77316,11 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BJ255" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="256">
       <c r="A256" t="inlineStr">
@@ -76167,6 +77442,11 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BJ256" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="257">
       <c r="A257" t="inlineStr">
@@ -76288,6 +77568,11 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BJ257" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="258">
       <c r="A258" t="inlineStr">
@@ -76409,6 +77694,11 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BJ258" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="259">
       <c r="A259" t="inlineStr">
@@ -76530,6 +77820,11 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BJ259" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/UATtracking.xlsx
+++ b/UATtracking.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BJ259"/>
+  <dimension ref="A1:BM259"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -739,6 +739,21 @@
           <t>0122</t>
         </is>
       </c>
+      <c r="BK1" s="1" t="inlineStr">
+        <is>
+          <t>0124</t>
+        </is>
+      </c>
+      <c r="BL1" s="1" t="inlineStr">
+        <is>
+          <t>0126</t>
+        </is>
+      </c>
+      <c r="BM1" s="1" t="inlineStr">
+        <is>
+          <t>0127</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -1045,6 +1060,21 @@
           <t>2error</t>
         </is>
       </c>
+      <c r="BK2" t="inlineStr">
+        <is>
+          <t>2error</t>
+        </is>
+      </c>
+      <c r="BL2" t="inlineStr">
+        <is>
+          <t>2error</t>
+        </is>
+      </c>
+      <c r="BM2" t="inlineStr">
+        <is>
+          <t>2error</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -1351,6 +1381,21 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BK3" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BL3" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BM3" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -1657,6 +1702,21 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BK4" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BL4" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BM4" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -1963,6 +2023,21 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BK5" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BL5" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BM5" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -2269,6 +2344,21 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BK6" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BL6" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BM6" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -2575,6 +2665,21 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BK7" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BL7" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BM7" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -2881,6 +2986,21 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BK8" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BL8" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BM8" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -3187,6 +3307,21 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BK9" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BL9" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BM9" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -3493,6 +3628,21 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BK10" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BL10" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BM10" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -3799,6 +3949,21 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BK11" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BL11" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BM11" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -4105,6 +4270,21 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BK12" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BL12" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BM12" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -4411,6 +4591,21 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BK13" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BL13" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BM13" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -4717,6 +4912,21 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BK14" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BL14" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BM14" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -5023,6 +5233,21 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BK15" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BL15" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BM15" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -5329,6 +5554,21 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BK16" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BL16" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BM16" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -5635,6 +5875,21 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BK17" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BL17" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BM17" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -5941,6 +6196,21 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BK18" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BL18" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BM18" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -6247,6 +6517,21 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BK19" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BL19" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BM19" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -6553,6 +6838,21 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BK20" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BL20" t="inlineStr">
+        <is>
+          <t>1error</t>
+        </is>
+      </c>
+      <c r="BM20" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -6859,6 +7159,21 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BK21" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BL21" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BM21" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -7165,6 +7480,21 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BK22" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BL22" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BM22" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -7471,6 +7801,21 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BK23" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BL23" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BM23" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -7777,6 +8122,21 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BK24" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BL24" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BM24" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -8083,6 +8443,21 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BK25" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BL25" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BM25" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -8094,10 +8469,8 @@
       <c r="C26" t="n">
         <v>2</v>
       </c>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="D26" t="n">
+        <v>2</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
@@ -8387,6 +8760,21 @@
       <c r="BJ26" t="inlineStr">
         <is>
           <t>online</t>
+        </is>
+      </c>
+      <c r="BK26" t="inlineStr">
+        <is>
+          <t>1error</t>
+        </is>
+      </c>
+      <c r="BL26" t="inlineStr">
+        <is>
+          <t>offline</t>
+        </is>
+      </c>
+      <c r="BM26" t="inlineStr">
+        <is>
+          <t>offline</t>
         </is>
       </c>
     </row>
@@ -8695,6 +9083,21 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BK27" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BL27" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BM27" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -9001,6 +9404,21 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BK28" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BL28" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BM28" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -9307,6 +9725,21 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BK29" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BL29" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BM29" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -9613,6 +10046,21 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BK30" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BL30" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BM30" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -9919,6 +10367,21 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BK31" t="inlineStr">
+        <is>
+          <t>1error</t>
+        </is>
+      </c>
+      <c r="BL31" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BM31" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -10225,6 +10688,21 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BK32" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BL32" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BM32" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -10531,6 +11009,21 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BK33" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BL33" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BM33" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -10837,6 +11330,21 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BK34" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BL34" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BM34" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -11141,6 +11649,21 @@
           <t>offline</t>
         </is>
       </c>
+      <c r="BK35" t="inlineStr">
+        <is>
+          <t>offline</t>
+        </is>
+      </c>
+      <c r="BL35" t="inlineStr">
+        <is>
+          <t>offline</t>
+        </is>
+      </c>
+      <c r="BM35" t="inlineStr">
+        <is>
+          <t>offline</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -11447,6 +11970,21 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BK36" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BL36" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BM36" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -11753,6 +12291,21 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BK37" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BL37" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BM37" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -12059,6 +12612,21 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BK38" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BL38" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BM38" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -12365,6 +12933,21 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BK39" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BL39" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BM39" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -12671,6 +13254,21 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BK40" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BL40" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BM40" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -12977,6 +13575,21 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BK41" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BL41" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BM41" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -13283,6 +13896,21 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BK42" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BL42" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BM42" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -13589,6 +14217,21 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BK43" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BL43" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BM43" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -13895,6 +14538,21 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BK44" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BL44" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BM44" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -14201,6 +14859,21 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BK45" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BL45" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BM45" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -14507,6 +15180,21 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BK46" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BL46" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BM46" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -14813,6 +15501,21 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BK47" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BL47" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BM47" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -15119,6 +15822,21 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BK48" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BL48" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BM48" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -15425,6 +16143,21 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BK49" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BL49" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BM49" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -15731,6 +16464,21 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BK50" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BL50" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BM50" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -16037,6 +16785,21 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BK51" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BL51" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BM51" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -16343,6 +17106,21 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BK52" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BL52" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BM52" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -16354,8 +17132,10 @@
       <c r="C53" t="n">
         <v>2</v>
       </c>
-      <c r="D53" t="n">
-        <v>2</v>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
@@ -16645,6 +17425,21 @@
       <c r="BJ53" t="inlineStr">
         <is>
           <t>offline</t>
+        </is>
+      </c>
+      <c r="BK53" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BL53" t="inlineStr">
+        <is>
+          <t>2error</t>
+        </is>
+      </c>
+      <c r="BM53" t="inlineStr">
+        <is>
+          <t>2error</t>
         </is>
       </c>
     </row>
@@ -16658,8 +17453,10 @@
       <c r="C54" t="n">
         <v>2</v>
       </c>
-      <c r="D54" t="n">
-        <v>2</v>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
@@ -16949,6 +17746,21 @@
       <c r="BJ54" t="inlineStr">
         <is>
           <t>offline</t>
+        </is>
+      </c>
+      <c r="BK54" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BL54" t="inlineStr">
+        <is>
+          <t>2error</t>
+        </is>
+      </c>
+      <c r="BM54" t="inlineStr">
+        <is>
+          <t>2error</t>
         </is>
       </c>
     </row>
@@ -17257,6 +18069,21 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BK55" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BL55" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BM55" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -17563,6 +18390,21 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BK56" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BL56" t="inlineStr">
+        <is>
+          <t>1error</t>
+        </is>
+      </c>
+      <c r="BM56" t="inlineStr">
+        <is>
+          <t>1error</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -17869,6 +18711,21 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BK57" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BL57" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BM57" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -18175,6 +19032,21 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BK58" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BL58" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BM58" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -18481,6 +19353,21 @@
           <t>1error</t>
         </is>
       </c>
+      <c r="BK59" t="inlineStr">
+        <is>
+          <t>1error</t>
+        </is>
+      </c>
+      <c r="BL59" t="inlineStr">
+        <is>
+          <t>1error</t>
+        </is>
+      </c>
+      <c r="BM59" t="inlineStr">
+        <is>
+          <t>1error</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -18787,6 +19674,21 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BK60" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BL60" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BM60" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -19093,6 +19995,21 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BK61" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BL61" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BM61" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -19399,6 +20316,21 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BK62" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BL62" t="inlineStr">
+        <is>
+          <t>1error</t>
+        </is>
+      </c>
+      <c r="BM62" t="inlineStr">
+        <is>
+          <t>1error</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -19705,6 +20637,21 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BK63" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BL63" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BM63" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -20011,6 +20958,21 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BK64" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BL64" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BM64" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -20317,6 +21279,21 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BK65" t="inlineStr">
+        <is>
+          <t>1error</t>
+        </is>
+      </c>
+      <c r="BL65" t="inlineStr">
+        <is>
+          <t>1error</t>
+        </is>
+      </c>
+      <c r="BM65" t="inlineStr">
+        <is>
+          <t>1error</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -20623,6 +21600,21 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BK66" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BL66" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BM66" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -20929,6 +21921,21 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BK67" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BL67" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BM67" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -21235,6 +22242,21 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BK68" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BL68" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BM68" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -21541,6 +22563,21 @@
           <t>2error</t>
         </is>
       </c>
+      <c r="BK69" t="inlineStr">
+        <is>
+          <t>2error</t>
+        </is>
+      </c>
+      <c r="BL69" t="inlineStr">
+        <is>
+          <t>2error</t>
+        </is>
+      </c>
+      <c r="BM69" t="inlineStr">
+        <is>
+          <t>2error</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -21847,6 +22884,21 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BK70" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BL70" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BM70" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -22153,6 +23205,21 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BK71" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BL71" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BM71" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -22459,6 +23526,21 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BK72" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BL72" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BM72" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -22765,6 +23847,21 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BK73" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BL73" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BM73" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -23071,6 +24168,21 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BK74" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BL74" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BM74" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -23377,6 +24489,21 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BK75" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BL75" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BM75" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -23683,6 +24810,21 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BK76" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BL76" t="inlineStr">
+        <is>
+          <t>1error</t>
+        </is>
+      </c>
+      <c r="BM76" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
@@ -23989,6 +25131,21 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BK77" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BL77" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BM77" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
@@ -24295,6 +25452,21 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BK78" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BL78" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BM78" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
@@ -24601,6 +25773,21 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BK79" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BL79" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BM79" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
@@ -24905,6 +26092,21 @@
           <t>offline</t>
         </is>
       </c>
+      <c r="BK80" t="inlineStr">
+        <is>
+          <t>offline</t>
+        </is>
+      </c>
+      <c r="BL80" t="inlineStr">
+        <is>
+          <t>offline</t>
+        </is>
+      </c>
+      <c r="BM80" t="inlineStr">
+        <is>
+          <t>offline</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
@@ -25211,6 +26413,21 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BK81" t="inlineStr">
+        <is>
+          <t>2error</t>
+        </is>
+      </c>
+      <c r="BL81" t="inlineStr">
+        <is>
+          <t>2error</t>
+        </is>
+      </c>
+      <c r="BM81" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
@@ -25517,6 +26734,21 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BK82" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BL82" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BM82" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
@@ -25823,6 +27055,21 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BK83" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BL83" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BM83" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
@@ -26129,6 +27376,21 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BK84" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BL84" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BM84" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
@@ -26435,6 +27697,21 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BK85" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BL85" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BM85" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
@@ -26741,6 +28018,21 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BK86" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BL86" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BM86" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
@@ -27047,6 +28339,21 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BK87" t="inlineStr">
+        <is>
+          <t>1error</t>
+        </is>
+      </c>
+      <c r="BL87" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BM87" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
@@ -27353,6 +28660,21 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BK88" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BL88" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BM88" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
@@ -27659,6 +28981,21 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BK89" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BL89" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BM89" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
@@ -27965,6 +29302,21 @@
           <t>2error</t>
         </is>
       </c>
+      <c r="BK90" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BL90" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BM90" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
@@ -28271,6 +29623,21 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BK91" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BL91" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BM91" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
@@ -28577,6 +29944,21 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BK92" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BL92" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BM92" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
@@ -28883,6 +30265,21 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BK93" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BL93" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BM93" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
@@ -29189,6 +30586,21 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BK94" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BL94" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BM94" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
@@ -29495,6 +30907,21 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BK95" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BL95" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BM95" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
@@ -29801,6 +31228,21 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BK96" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BL96" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BM96" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
@@ -30107,6 +31549,21 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BK97" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BL97" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BM97" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
@@ -30413,6 +31870,21 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BK98" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BL98" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BM98" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
@@ -30424,8 +31896,10 @@
       <c r="C99" t="n">
         <v>2</v>
       </c>
-      <c r="D99" t="n">
-        <v>2</v>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
@@ -30715,6 +32189,21 @@
       <c r="BJ99" t="inlineStr">
         <is>
           <t>offline</t>
+        </is>
+      </c>
+      <c r="BK99" t="inlineStr">
+        <is>
+          <t>2error</t>
+        </is>
+      </c>
+      <c r="BL99" t="inlineStr">
+        <is>
+          <t>2error</t>
+        </is>
+      </c>
+      <c r="BM99" t="inlineStr">
+        <is>
+          <t>2error</t>
         </is>
       </c>
     </row>
@@ -31023,6 +32512,21 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BK100" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BL100" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BM100" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
@@ -31329,6 +32833,21 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BK101" t="inlineStr">
+        <is>
+          <t>1error</t>
+        </is>
+      </c>
+      <c r="BL101" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BM101" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
@@ -31635,6 +33154,21 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BK102" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BL102" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BM102" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
@@ -31941,6 +33475,21 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BK103" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BL103" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BM103" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
@@ -32247,6 +33796,21 @@
           <t>2error</t>
         </is>
       </c>
+      <c r="BK104" t="inlineStr">
+        <is>
+          <t>2error</t>
+        </is>
+      </c>
+      <c r="BL104" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BM104" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
@@ -32553,6 +34117,21 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BK105" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BL105" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BM105" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
@@ -32564,10 +34143,8 @@
       <c r="C106" t="n">
         <v>2</v>
       </c>
-      <c r="D106" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="D106" t="n">
+        <v>2</v>
       </c>
       <c r="E106" t="inlineStr">
         <is>
@@ -32857,6 +34434,21 @@
       <c r="BJ106" t="inlineStr">
         <is>
           <t>online</t>
+        </is>
+      </c>
+      <c r="BK106" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BL106" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BM106" t="inlineStr">
+        <is>
+          <t>offline</t>
         </is>
       </c>
     </row>
@@ -33165,6 +34757,21 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BK107" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BL107" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BM107" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
@@ -33471,6 +35078,21 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BK108" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BL108" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BM108" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
@@ -33777,6 +35399,21 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BK109" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BL109" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BM109" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
@@ -34083,6 +35720,21 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BK110" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BL110" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BM110" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
@@ -34389,6 +36041,21 @@
           <t>1error</t>
         </is>
       </c>
+      <c r="BK111" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BL111" t="inlineStr">
+        <is>
+          <t>1error</t>
+        </is>
+      </c>
+      <c r="BM111" t="inlineStr">
+        <is>
+          <t>1error</t>
+        </is>
+      </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
@@ -34695,6 +36362,21 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BK112" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BL112" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BM112" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
@@ -35001,6 +36683,21 @@
           <t>1error</t>
         </is>
       </c>
+      <c r="BK113" t="inlineStr">
+        <is>
+          <t>1error</t>
+        </is>
+      </c>
+      <c r="BL113" t="inlineStr">
+        <is>
+          <t>1error</t>
+        </is>
+      </c>
+      <c r="BM113" t="inlineStr">
+        <is>
+          <t>1error</t>
+        </is>
+      </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
@@ -35307,6 +37004,21 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BK114" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BL114" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BM114" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
@@ -35613,6 +37325,21 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BK115" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BL115" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BM115" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
@@ -35919,6 +37646,21 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BK116" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BL116" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BM116" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
@@ -36223,6 +37965,21 @@
           <t>offline</t>
         </is>
       </c>
+      <c r="BK117" t="inlineStr">
+        <is>
+          <t>offline</t>
+        </is>
+      </c>
+      <c r="BL117" t="inlineStr">
+        <is>
+          <t>offline</t>
+        </is>
+      </c>
+      <c r="BM117" t="inlineStr">
+        <is>
+          <t>offline</t>
+        </is>
+      </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
@@ -36529,6 +38286,21 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BK118" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BL118" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BM118" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
@@ -36833,6 +38605,21 @@
           <t>offline</t>
         </is>
       </c>
+      <c r="BK119" t="inlineStr">
+        <is>
+          <t>offline</t>
+        </is>
+      </c>
+      <c r="BL119" t="inlineStr">
+        <is>
+          <t>offline</t>
+        </is>
+      </c>
+      <c r="BM119" t="inlineStr">
+        <is>
+          <t>offline</t>
+        </is>
+      </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
@@ -37139,6 +38926,21 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BK120" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BL120" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BM120" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
@@ -37445,6 +39247,21 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BK121" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BL121" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BM121" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
@@ -37751,6 +39568,21 @@
           <t>1error</t>
         </is>
       </c>
+      <c r="BK122" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BL122" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BM122" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
@@ -38057,6 +39889,21 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BK123" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BL123" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BM123" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
@@ -38363,6 +40210,21 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BK124" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BL124" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BM124" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
@@ -38669,6 +40531,21 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BK125" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BL125" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BM125" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
@@ -38973,6 +40850,21 @@
           <t>offline</t>
         </is>
       </c>
+      <c r="BK126" t="inlineStr">
+        <is>
+          <t>offline</t>
+        </is>
+      </c>
+      <c r="BL126" t="inlineStr">
+        <is>
+          <t>offline</t>
+        </is>
+      </c>
+      <c r="BM126" t="inlineStr">
+        <is>
+          <t>offline</t>
+        </is>
+      </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
@@ -39279,6 +41171,21 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BK127" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BL127" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BM127" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
@@ -39585,6 +41492,21 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BK128" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BL128" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BM128" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
@@ -39891,6 +41813,21 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BK129" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BL129" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BM129" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
@@ -40197,6 +42134,21 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BK130" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BL130" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BM130" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
@@ -40503,6 +42455,21 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BK131" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BL131" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BM131" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
@@ -40809,6 +42776,21 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BK132" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BL132" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BM132" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
@@ -41113,6 +43095,21 @@
           <t>offline</t>
         </is>
       </c>
+      <c r="BK133" t="inlineStr">
+        <is>
+          <t>offline</t>
+        </is>
+      </c>
+      <c r="BL133" t="inlineStr">
+        <is>
+          <t>offline</t>
+        </is>
+      </c>
+      <c r="BM133" t="inlineStr">
+        <is>
+          <t>offline</t>
+        </is>
+      </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
@@ -41419,6 +43416,21 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BK134" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BL134" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BM134" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
@@ -41725,6 +43737,21 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BK135" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BL135" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BM135" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
@@ -42031,6 +44058,21 @@
           <t>1error</t>
         </is>
       </c>
+      <c r="BK136" t="inlineStr">
+        <is>
+          <t>1error</t>
+        </is>
+      </c>
+      <c r="BL136" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BM136" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
@@ -42337,6 +44379,21 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BK137" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BL137" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BM137" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
@@ -42641,6 +44698,21 @@
           <t>offline</t>
         </is>
       </c>
+      <c r="BK138" t="inlineStr">
+        <is>
+          <t>offline</t>
+        </is>
+      </c>
+      <c r="BL138" t="inlineStr">
+        <is>
+          <t>offline</t>
+        </is>
+      </c>
+      <c r="BM138" t="inlineStr">
+        <is>
+          <t>offline</t>
+        </is>
+      </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
@@ -42947,6 +45019,21 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BK139" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BL139" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BM139" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
@@ -43253,6 +45340,21 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BK140" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BL140" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BM140" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
@@ -43559,6 +45661,21 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BK141" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BL141" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BM141" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
@@ -43865,6 +45982,21 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BK142" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BL142" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BM142" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
@@ -44171,6 +46303,21 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BK143" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BL143" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BM143" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
@@ -44477,6 +46624,21 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BK144" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BL144" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BM144" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
@@ -44783,6 +46945,21 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BK145" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BL145" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BM145" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
@@ -45089,6 +47266,21 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BK146" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BL146" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BM146" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
@@ -45395,6 +47587,21 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BK147" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BL147" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BM147" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
@@ -45701,6 +47908,21 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BK148" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BL148" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BM148" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
@@ -46007,6 +48229,21 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BK149" t="inlineStr">
+        <is>
+          <t>1error</t>
+        </is>
+      </c>
+      <c r="BL149" t="inlineStr">
+        <is>
+          <t>1error</t>
+        </is>
+      </c>
+      <c r="BM149" t="inlineStr">
+        <is>
+          <t>1error</t>
+        </is>
+      </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
@@ -46313,6 +48550,21 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BK150" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BL150" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BM150" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
@@ -46619,6 +48871,21 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BK151" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BL151" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BM151" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
@@ -46923,6 +49190,21 @@
           <t>offline</t>
         </is>
       </c>
+      <c r="BK152" t="inlineStr">
+        <is>
+          <t>offline</t>
+        </is>
+      </c>
+      <c r="BL152" t="inlineStr">
+        <is>
+          <t>offline</t>
+        </is>
+      </c>
+      <c r="BM152" t="inlineStr">
+        <is>
+          <t>offline</t>
+        </is>
+      </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
@@ -47229,6 +49511,21 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BK153" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BL153" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BM153" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
@@ -47535,6 +49832,21 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BK154" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BL154" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BM154" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
@@ -47841,6 +50153,21 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BK155" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BL155" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BM155" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
@@ -47854,7 +50181,7 @@
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="E156" t="inlineStr">
@@ -48143,6 +50470,21 @@
         </is>
       </c>
       <c r="BJ156" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BK156" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BL156" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BM156" t="inlineStr">
         <is>
           <t>online</t>
         </is>
@@ -48453,6 +50795,21 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BK157" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BL157" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BM157" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
@@ -48759,6 +51116,21 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BK158" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BL158" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BM158" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
@@ -49065,6 +51437,21 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BK159" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BL159" t="inlineStr">
+        <is>
+          <t>1error</t>
+        </is>
+      </c>
+      <c r="BM159" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
@@ -49371,6 +51758,21 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BK160" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BL160" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BM160" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
@@ -49677,6 +52079,21 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BK161" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BL161" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BM161" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
@@ -49983,6 +52400,21 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BK162" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BL162" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BM162" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
@@ -50289,6 +52721,21 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BK163" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BL163" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BM163" t="inlineStr">
+        <is>
+          <t>2error</t>
+        </is>
+      </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
@@ -50595,6 +53042,21 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BK164" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BL164" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BM164" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
@@ -50901,6 +53363,21 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BK165" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BL165" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BM165" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
@@ -51207,6 +53684,21 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BK166" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BL166" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BM166" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
@@ -51513,6 +54005,21 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BK167" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BL167" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BM167" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
@@ -51817,6 +54324,21 @@
           <t>offline</t>
         </is>
       </c>
+      <c r="BK168" t="inlineStr">
+        <is>
+          <t>offline</t>
+        </is>
+      </c>
+      <c r="BL168" t="inlineStr">
+        <is>
+          <t>offline</t>
+        </is>
+      </c>
+      <c r="BM168" t="inlineStr">
+        <is>
+          <t>offline</t>
+        </is>
+      </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
@@ -52123,6 +54645,21 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BK169" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BL169" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BM169" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
@@ -52429,6 +54966,21 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BK170" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BL170" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BM170" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
@@ -52735,6 +55287,21 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BK171" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BL171" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BM171" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
@@ -53041,6 +55608,21 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BK172" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BL172" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BM172" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
@@ -53347,6 +55929,21 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BK173" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BL173" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BM173" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
@@ -53653,6 +56250,21 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BK174" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BL174" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BM174" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
@@ -53959,6 +56571,21 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BK175" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BL175" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BM175" t="inlineStr">
+        <is>
+          <t>1error</t>
+        </is>
+      </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
@@ -54265,6 +56892,21 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BK176" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BL176" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BM176" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
@@ -54569,6 +57211,21 @@
           <t>offline</t>
         </is>
       </c>
+      <c r="BK177" t="inlineStr">
+        <is>
+          <t>offline</t>
+        </is>
+      </c>
+      <c r="BL177" t="inlineStr">
+        <is>
+          <t>offline</t>
+        </is>
+      </c>
+      <c r="BM177" t="inlineStr">
+        <is>
+          <t>offline</t>
+        </is>
+      </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
@@ -54875,6 +57532,21 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BK178" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BL178" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BM178" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
@@ -55181,6 +57853,21 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BK179" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BL179" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BM179" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
@@ -55487,6 +58174,21 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BK180" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BL180" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BM180" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
@@ -55793,6 +58495,21 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BK181" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BL181" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BM181" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
@@ -56097,6 +58814,21 @@
           <t>offline</t>
         </is>
       </c>
+      <c r="BK182" t="inlineStr">
+        <is>
+          <t>offline</t>
+        </is>
+      </c>
+      <c r="BL182" t="inlineStr">
+        <is>
+          <t>offline</t>
+        </is>
+      </c>
+      <c r="BM182" t="inlineStr">
+        <is>
+          <t>offline</t>
+        </is>
+      </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
@@ -56403,6 +59135,21 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BK183" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BL183" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BM183" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
@@ -56709,6 +59456,21 @@
           <t>1error</t>
         </is>
       </c>
+      <c r="BK184" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BL184" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BM184" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
@@ -57015,6 +59777,21 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BK185" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BL185" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BM185" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
@@ -57321,6 +60098,21 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BK186" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BL186" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BM186" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
@@ -57627,6 +60419,21 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BK187" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BL187" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BM187" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
@@ -57931,6 +60738,21 @@
           <t>offline</t>
         </is>
       </c>
+      <c r="BK188" t="inlineStr">
+        <is>
+          <t>offline</t>
+        </is>
+      </c>
+      <c r="BL188" t="inlineStr">
+        <is>
+          <t>offline</t>
+        </is>
+      </c>
+      <c r="BM188" t="inlineStr">
+        <is>
+          <t>offline</t>
+        </is>
+      </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
@@ -58237,6 +61059,21 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BK189" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BL189" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BM189" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
@@ -58543,6 +61380,21 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BK190" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BL190" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BM190" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
@@ -58849,6 +61701,21 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BK191" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BL191" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BM191" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
@@ -59155,6 +62022,21 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BK192" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BL192" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BM192" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
@@ -59461,6 +62343,21 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BK193" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BL193" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BM193" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
@@ -59767,6 +62664,21 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BK194" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BL194" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BM194" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
@@ -60073,6 +62985,21 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BK195" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BL195" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BM195" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
@@ -60379,6 +63306,21 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BK196" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BL196" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BM196" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
@@ -60685,6 +63627,21 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BK197" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BL197" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BM197" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
@@ -60991,6 +63948,21 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BK198" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BL198" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BM198" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
@@ -61297,6 +64269,21 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BK199" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BL199" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BM199" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
@@ -61603,6 +64590,21 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BK200" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BL200" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BM200" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
@@ -61909,6 +64911,21 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BK201" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BL201" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BM201" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
@@ -62215,6 +65232,21 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BK202" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BL202" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BM202" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
@@ -62521,6 +65553,21 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BK203" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BL203" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BM203" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
@@ -62827,6 +65874,21 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BK204" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BL204" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BM204" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
@@ -63133,6 +66195,21 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BK205" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BL205" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BM205" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
@@ -63439,6 +66516,21 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BK206" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BL206" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BM206" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
@@ -63745,6 +66837,21 @@
           <t>1error</t>
         </is>
       </c>
+      <c r="BK207" t="inlineStr">
+        <is>
+          <t>1error</t>
+        </is>
+      </c>
+      <c r="BL207" t="inlineStr">
+        <is>
+          <t>1error</t>
+        </is>
+      </c>
+      <c r="BM207" t="inlineStr">
+        <is>
+          <t>1error</t>
+        </is>
+      </c>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
@@ -64051,6 +67158,21 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BK208" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BL208" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BM208" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
@@ -64357,6 +67479,21 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BK209" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BL209" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BM209" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
@@ -64663,6 +67800,21 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BK210" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BL210" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BM210" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
@@ -64969,6 +68121,21 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BK211" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BL211" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BM211" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
@@ -65275,6 +68442,21 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BK212" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BL212" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BM212" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
@@ -65581,6 +68763,21 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BK213" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BL213" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BM213" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
@@ -65887,6 +69084,21 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BK214" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BL214" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BM214" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
@@ -66193,6 +69405,21 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BK215" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BL215" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BM215" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
@@ -66499,6 +69726,21 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BK216" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BL216" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BM216" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
@@ -66805,6 +70047,21 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BK217" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BL217" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BM217" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
@@ -67111,6 +70368,21 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BK218" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BL218" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BM218" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
@@ -67417,6 +70689,21 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BK219" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BL219" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BM219" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
@@ -67723,6 +71010,21 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BK220" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BL220" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BM220" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="221">
       <c r="A221" t="inlineStr">
@@ -68029,6 +71331,21 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BK221" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BL221" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BM221" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="222">
       <c r="A222" t="inlineStr">
@@ -68335,6 +71652,21 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BK222" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BL222" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BM222" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr">
@@ -68641,6 +71973,21 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BK223" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BL223" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BM223" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="224">
       <c r="A224" t="inlineStr">
@@ -68947,6 +72294,21 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BK224" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BL224" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BM224" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="225">
       <c r="A225" t="inlineStr">
@@ -69253,6 +72615,21 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BK225" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BL225" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BM225" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="226">
       <c r="A226" t="inlineStr">
@@ -69559,6 +72936,21 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BK226" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BL226" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BM226" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="227">
       <c r="A227" t="inlineStr">
@@ -69865,6 +73257,21 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BK227" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BL227" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BM227" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="228">
       <c r="A228" t="inlineStr">
@@ -70171,6 +73578,21 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BK228" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BL228" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BM228" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="229">
       <c r="A229" t="inlineStr">
@@ -70477,6 +73899,21 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BK229" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BL229" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BM229" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="230">
       <c r="A230" t="inlineStr">
@@ -70783,6 +74220,21 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BK230" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BL230" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BM230" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="231">
       <c r="A231" t="inlineStr">
@@ -71089,6 +74541,21 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BK231" t="inlineStr">
+        <is>
+          <t>1error</t>
+        </is>
+      </c>
+      <c r="BL231" t="inlineStr">
+        <is>
+          <t>1error</t>
+        </is>
+      </c>
+      <c r="BM231" t="inlineStr">
+        <is>
+          <t>1error</t>
+        </is>
+      </c>
     </row>
     <row r="232">
       <c r="A232" t="inlineStr">
@@ -71395,6 +74862,21 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BK232" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BL232" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BM232" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="233">
       <c r="A233" t="inlineStr">
@@ -71701,6 +75183,21 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BK233" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BL233" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BM233" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="234">
       <c r="A234" t="inlineStr">
@@ -72007,6 +75504,21 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BK234" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BL234" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BM234" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="235">
       <c r="A235" t="inlineStr">
@@ -72313,6 +75825,21 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BK235" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BL235" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BM235" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="236">
       <c r="A236" t="inlineStr">
@@ -72619,6 +76146,21 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BK236" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BL236" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BM236" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="237">
       <c r="A237" t="inlineStr">
@@ -72925,6 +76467,21 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BK237" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BL237" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BM237" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="238">
       <c r="A238" t="inlineStr">
@@ -73231,6 +76788,21 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BK238" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BL238" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BM238" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="239">
       <c r="A239" t="inlineStr">
@@ -73537,6 +77109,21 @@
           <t>1error</t>
         </is>
       </c>
+      <c r="BK239" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BL239" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BM239" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="240">
       <c r="A240" t="inlineStr">
@@ -73843,6 +77430,21 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BK240" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BL240" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BM240" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="241">
       <c r="A241" t="inlineStr">
@@ -74149,6 +77751,21 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BK241" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BL241" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BM241" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="242">
       <c r="A242" t="inlineStr">
@@ -74455,6 +78072,21 @@
           <t>1error</t>
         </is>
       </c>
+      <c r="BK242" t="inlineStr">
+        <is>
+          <t>1error</t>
+        </is>
+      </c>
+      <c r="BL242" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BM242" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="243">
       <c r="A243" t="inlineStr">
@@ -74761,6 +78393,21 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BK243" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BL243" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BM243" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="244">
       <c r="A244" t="inlineStr">
@@ -75063,6 +78710,21 @@
         </is>
       </c>
       <c r="BJ244" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BK244" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BL244" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BM244" t="inlineStr">
         <is>
           <t>online</t>
         </is>
@@ -75337,6 +78999,21 @@
         </is>
       </c>
       <c r="BJ245" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BK245" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BL245" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BM245" t="inlineStr">
         <is>
           <t>online</t>
         </is>
@@ -75583,6 +79260,21 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BK246" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BL246" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BM246" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="247">
       <c r="A247" t="inlineStr">
@@ -75821,6 +79513,21 @@
         </is>
       </c>
       <c r="BJ247" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BK247" t="inlineStr">
+        <is>
+          <t>1error</t>
+        </is>
+      </c>
+      <c r="BL247" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BM247" t="inlineStr">
         <is>
           <t>online</t>
         </is>
@@ -76035,6 +79742,21 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BK248" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BL248" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BM248" t="inlineStr">
+        <is>
+          <t>1error</t>
+        </is>
+      </c>
     </row>
     <row r="249">
       <c r="A249" t="inlineStr">
@@ -76241,6 +79963,21 @@
         </is>
       </c>
       <c r="BJ249" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BK249" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BL249" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BM249" t="inlineStr">
         <is>
           <t>online</t>
         </is>
@@ -76451,6 +80188,21 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BK250" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BL250" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BM250" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="251">
       <c r="A251" t="inlineStr">
@@ -76657,6 +80409,21 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BK251" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BL251" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BM251" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="252">
       <c r="A252" t="inlineStr">
@@ -76863,6 +80630,21 @@
           <t>1error</t>
         </is>
       </c>
+      <c r="BK252" t="inlineStr">
+        <is>
+          <t>1error</t>
+        </is>
+      </c>
+      <c r="BL252" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BM252" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="253">
       <c r="A253" t="inlineStr">
@@ -77065,6 +80847,21 @@
         </is>
       </c>
       <c r="BJ253" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BK253" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BL253" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BM253" t="inlineStr">
         <is>
           <t>online</t>
         </is>
@@ -77195,6 +80992,21 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BK254" t="inlineStr">
+        <is>
+          <t>2error</t>
+        </is>
+      </c>
+      <c r="BL254" t="inlineStr">
+        <is>
+          <t>2error</t>
+        </is>
+      </c>
+      <c r="BM254" t="inlineStr">
+        <is>
+          <t>2error</t>
+        </is>
+      </c>
     </row>
     <row r="255">
       <c r="A255" t="inlineStr">
@@ -77321,6 +81133,21 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BK255" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BL255" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BM255" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="256">
       <c r="A256" t="inlineStr">
@@ -77447,6 +81274,21 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BK256" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BL256" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BM256" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="257">
       <c r="A257" t="inlineStr">
@@ -77573,6 +81415,21 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BK257" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BL257" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BM257" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="258">
       <c r="A258" t="inlineStr">
@@ -77699,6 +81556,21 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BK258" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BL258" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BM258" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="259">
       <c r="A259" t="inlineStr">
@@ -77825,6 +81697,21 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BK259" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BL259" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BM259" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/UATtracking.xlsx
+++ b/UATtracking.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BM259"/>
+  <dimension ref="A1:BN259"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -754,6 +754,11 @@
           <t>0127</t>
         </is>
       </c>
+      <c r="BN1" s="1" t="inlineStr">
+        <is>
+          <t>0211</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -1075,6 +1080,11 @@
           <t>2error</t>
         </is>
       </c>
+      <c r="BN2" t="inlineStr">
+        <is>
+          <t>2error</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -1396,6 +1406,11 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BN3" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -1717,6 +1732,11 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BN4" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -2038,6 +2058,11 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BN5" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -2359,6 +2384,11 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BN6" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -2680,6 +2710,11 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BN7" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -3001,6 +3036,11 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BN8" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -3322,6 +3362,11 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BN9" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -3643,6 +3688,11 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BN10" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -3964,6 +4014,11 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BN11" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -4285,6 +4340,11 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BN12" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -4606,6 +4666,11 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BN13" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -4927,6 +4992,11 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BN14" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -5248,6 +5318,11 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BN15" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -5569,6 +5644,11 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BN16" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -5890,6 +5970,11 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BN17" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -6211,6 +6296,11 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BN18" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -6532,6 +6622,11 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BN19" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -6853,6 +6948,11 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BN20" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -7174,6 +7274,11 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BN21" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -7495,6 +7600,11 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BN22" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -7816,6 +7926,11 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BN23" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -8137,6 +8252,11 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BN24" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -8458,6 +8578,11 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BN25" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -8469,8 +8594,10 @@
       <c r="C26" t="n">
         <v>2</v>
       </c>
-      <c r="D26" t="n">
-        <v>2</v>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
@@ -8775,6 +8902,11 @@
       <c r="BM26" t="inlineStr">
         <is>
           <t>offline</t>
+        </is>
+      </c>
+      <c r="BN26" t="inlineStr">
+        <is>
+          <t>online</t>
         </is>
       </c>
     </row>
@@ -9098,6 +9230,11 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BN27" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -9419,6 +9556,11 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BN28" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -9740,6 +9882,11 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BN29" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -10061,6 +10208,11 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BN30" t="inlineStr">
+        <is>
+          <t>1error</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -10382,6 +10534,11 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BN31" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -10703,6 +10860,11 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BN32" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -11024,6 +11186,11 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BN33" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -11345,6 +11512,11 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BN34" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -11664,6 +11836,11 @@
           <t>offline</t>
         </is>
       </c>
+      <c r="BN35" t="inlineStr">
+        <is>
+          <t>offline</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -11985,6 +12162,11 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BN36" t="inlineStr">
+        <is>
+          <t>2error</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -12306,6 +12488,11 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BN37" t="inlineStr">
+        <is>
+          <t>1error</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -12627,6 +12814,11 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BN38" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -12948,6 +13140,11 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BN39" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -13269,6 +13466,11 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BN40" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -13590,6 +13792,11 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BN41" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -13911,6 +14118,11 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BN42" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -14232,6 +14444,11 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BN43" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -14553,6 +14770,11 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BN44" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -14874,6 +15096,11 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BN45" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -15195,6 +15422,11 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BN46" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -15516,6 +15748,11 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BN47" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -15837,6 +16074,11 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BN48" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -16158,6 +16400,11 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BN49" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -16479,6 +16726,11 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BN50" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -16800,6 +17052,11 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BN51" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -17121,6 +17378,11 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BN52" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -17132,10 +17394,8 @@
       <c r="C53" t="n">
         <v>2</v>
       </c>
-      <c r="D53" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="D53" t="n">
+        <v>2</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
@@ -17440,6 +17700,11 @@
       <c r="BM53" t="inlineStr">
         <is>
           <t>2error</t>
+        </is>
+      </c>
+      <c r="BN53" t="inlineStr">
+        <is>
+          <t>offline</t>
         </is>
       </c>
     </row>
@@ -17453,10 +17718,8 @@
       <c r="C54" t="n">
         <v>2</v>
       </c>
-      <c r="D54" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="D54" t="n">
+        <v>2</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
@@ -17761,6 +18024,11 @@
       <c r="BM54" t="inlineStr">
         <is>
           <t>2error</t>
+        </is>
+      </c>
+      <c r="BN54" t="inlineStr">
+        <is>
+          <t>offline</t>
         </is>
       </c>
     </row>
@@ -18084,6 +18352,11 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BN55" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -18405,6 +18678,11 @@
           <t>1error</t>
         </is>
       </c>
+      <c r="BN56" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -18726,6 +19004,11 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BN57" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -19047,6 +19330,11 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BN58" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -19060,7 +19348,7 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
@@ -19366,6 +19654,11 @@
       <c r="BM59" t="inlineStr">
         <is>
           <t>1error</t>
+        </is>
+      </c>
+      <c r="BN59" t="inlineStr">
+        <is>
+          <t>online</t>
         </is>
       </c>
     </row>
@@ -19689,6 +19982,11 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BN60" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -20010,6 +20308,11 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BN61" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -20331,6 +20634,11 @@
           <t>1error</t>
         </is>
       </c>
+      <c r="BN62" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -20652,6 +20960,11 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BN63" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -20973,6 +21286,11 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BN64" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -21294,6 +21612,11 @@
           <t>1error</t>
         </is>
       </c>
+      <c r="BN65" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -21615,6 +21938,11 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BN66" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -21936,6 +22264,11 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BN67" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -22257,6 +22590,11 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BN68" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -22578,6 +22916,11 @@
           <t>2error</t>
         </is>
       </c>
+      <c r="BN69" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -22899,6 +23242,11 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BN70" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -23220,6 +23568,11 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BN71" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -23541,6 +23894,11 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BN72" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -23862,6 +24220,11 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BN73" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -24183,6 +24546,11 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BN74" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -24504,6 +24872,11 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BN75" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -24825,6 +25198,11 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BN76" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
@@ -25146,6 +25524,11 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BN77" t="inlineStr">
+        <is>
+          <t>1error</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
@@ -25467,6 +25850,11 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BN78" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
@@ -25480,7 +25868,7 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
@@ -25784,6 +26172,11 @@
         </is>
       </c>
       <c r="BM79" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BN79" t="inlineStr">
         <is>
           <t>online</t>
         </is>
@@ -26107,6 +26500,11 @@
           <t>offline</t>
         </is>
       </c>
+      <c r="BN80" t="inlineStr">
+        <is>
+          <t>offline</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
@@ -26428,6 +26826,11 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BN81" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
@@ -26749,6 +27152,11 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BN82" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
@@ -27070,6 +27478,11 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BN83" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
@@ -27391,6 +27804,11 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BN84" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
@@ -27712,6 +28130,11 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BN85" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
@@ -28033,6 +28456,11 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BN86" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
@@ -28046,7 +28474,7 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
@@ -28350,6 +28778,11 @@
         </is>
       </c>
       <c r="BM87" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BN87" t="inlineStr">
         <is>
           <t>online</t>
         </is>
@@ -28675,6 +29108,11 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BN88" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
@@ -28996,6 +29434,11 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BN89" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
@@ -29317,6 +29760,11 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BN90" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
@@ -29638,6 +30086,11 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BN91" t="inlineStr">
+        <is>
+          <t>1error</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
@@ -29959,6 +30412,11 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BN92" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
@@ -30280,6 +30738,11 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BN93" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
@@ -30601,6 +31064,11 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BN94" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
@@ -30614,7 +31082,7 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
@@ -30918,6 +31386,11 @@
         </is>
       </c>
       <c r="BM95" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BN95" t="inlineStr">
         <is>
           <t>online</t>
         </is>
@@ -31243,6 +31716,11 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BN96" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
@@ -31564,6 +32042,11 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BN97" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
@@ -31885,6 +32368,11 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BN98" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
@@ -31896,10 +32384,8 @@
       <c r="C99" t="n">
         <v>2</v>
       </c>
-      <c r="D99" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="D99" t="n">
+        <v>2</v>
       </c>
       <c r="E99" t="inlineStr">
         <is>
@@ -32204,6 +32690,11 @@
       <c r="BM99" t="inlineStr">
         <is>
           <t>2error</t>
+        </is>
+      </c>
+      <c r="BN99" t="inlineStr">
+        <is>
+          <t>offline</t>
         </is>
       </c>
     </row>
@@ -32527,6 +33018,11 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BN100" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
@@ -32848,6 +33344,11 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BN101" t="inlineStr">
+        <is>
+          <t>2error</t>
+        </is>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
@@ -33169,6 +33670,11 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BN102" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
@@ -33490,6 +33996,11 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BN103" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
@@ -33811,6 +34322,11 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BN104" t="inlineStr">
+        <is>
+          <t>1error</t>
+        </is>
+      </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
@@ -34132,6 +34648,11 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BN105" t="inlineStr">
+        <is>
+          <t>2error</t>
+        </is>
+      </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
@@ -34143,8 +34664,10 @@
       <c r="C106" t="n">
         <v>2</v>
       </c>
-      <c r="D106" t="n">
-        <v>2</v>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
@@ -34449,6 +34972,11 @@
       <c r="BM106" t="inlineStr">
         <is>
           <t>offline</t>
+        </is>
+      </c>
+      <c r="BN106" t="inlineStr">
+        <is>
+          <t>online</t>
         </is>
       </c>
     </row>
@@ -34462,10 +34990,8 @@
       <c r="C107" t="n">
         <v>2</v>
       </c>
-      <c r="D107" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="D107" t="n">
+        <v>2</v>
       </c>
       <c r="E107" t="inlineStr">
         <is>
@@ -34770,6 +35296,11 @@
       <c r="BM107" t="inlineStr">
         <is>
           <t>online</t>
+        </is>
+      </c>
+      <c r="BN107" t="inlineStr">
+        <is>
+          <t>offline</t>
         </is>
       </c>
     </row>
@@ -35093,6 +35624,11 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BN108" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
@@ -35414,6 +35950,11 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BN109" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
@@ -35735,6 +36276,11 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BN110" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
@@ -36056,6 +36602,11 @@
           <t>1error</t>
         </is>
       </c>
+      <c r="BN111" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
@@ -36377,6 +36928,11 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BN112" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
@@ -36390,7 +36946,7 @@
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
@@ -36696,6 +37252,11 @@
       <c r="BM113" t="inlineStr">
         <is>
           <t>1error</t>
+        </is>
+      </c>
+      <c r="BN113" t="inlineStr">
+        <is>
+          <t>online</t>
         </is>
       </c>
     </row>
@@ -37019,6 +37580,11 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BN114" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
@@ -37340,6 +37906,11 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BN115" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
@@ -37661,6 +38232,11 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BN116" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
@@ -37980,6 +38556,11 @@
           <t>offline</t>
         </is>
       </c>
+      <c r="BN117" t="inlineStr">
+        <is>
+          <t>offline</t>
+        </is>
+      </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
@@ -38301,6 +38882,11 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BN118" t="inlineStr">
+        <is>
+          <t>1error</t>
+        </is>
+      </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
@@ -38620,6 +39206,11 @@
           <t>offline</t>
         </is>
       </c>
+      <c r="BN119" t="inlineStr">
+        <is>
+          <t>offline</t>
+        </is>
+      </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
@@ -38941,6 +39532,11 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BN120" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
@@ -39262,6 +39858,11 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BN121" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
@@ -39583,6 +40184,11 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BN122" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
@@ -39904,6 +40510,11 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BN123" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
@@ -40225,6 +40836,11 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BN124" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
@@ -40546,6 +41162,11 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BN125" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
@@ -40865,6 +41486,11 @@
           <t>offline</t>
         </is>
       </c>
+      <c r="BN126" t="inlineStr">
+        <is>
+          <t>offline</t>
+        </is>
+      </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
@@ -41186,6 +41812,11 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BN127" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
@@ -41507,6 +42138,11 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BN128" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
@@ -41828,6 +42464,11 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BN129" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
@@ -42149,6 +42790,11 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BN130" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
@@ -42470,6 +43116,11 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BN131" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
@@ -42791,6 +43442,11 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BN132" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
@@ -43110,6 +43766,11 @@
           <t>offline</t>
         </is>
       </c>
+      <c r="BN133" t="inlineStr">
+        <is>
+          <t>offline</t>
+        </is>
+      </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
@@ -43431,6 +44092,11 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BN134" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
@@ -43752,6 +44418,11 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BN135" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
@@ -44073,6 +44744,11 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BN136" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
@@ -44394,6 +45070,11 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BN137" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
@@ -44713,6 +45394,11 @@
           <t>offline</t>
         </is>
       </c>
+      <c r="BN138" t="inlineStr">
+        <is>
+          <t>offline</t>
+        </is>
+      </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
@@ -45034,6 +45720,11 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BN139" t="inlineStr">
+        <is>
+          <t>1error</t>
+        </is>
+      </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
@@ -45355,6 +46046,11 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BN140" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
@@ -45676,6 +46372,11 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BN141" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
@@ -45997,6 +46698,11 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BN142" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
@@ -46318,6 +47024,11 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BN143" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
@@ -46639,6 +47350,11 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BN144" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
@@ -46960,6 +47676,11 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BN145" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
@@ -47281,6 +48002,11 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BN146" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
@@ -47602,6 +48328,11 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BN147" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
@@ -47923,6 +48654,11 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BN148" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
@@ -48244,6 +48980,11 @@
           <t>1error</t>
         </is>
       </c>
+      <c r="BN149" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
@@ -48565,6 +49306,11 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BN150" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
@@ -48886,6 +49632,11 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BN151" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
@@ -49205,6 +49956,11 @@
           <t>offline</t>
         </is>
       </c>
+      <c r="BN152" t="inlineStr">
+        <is>
+          <t>offline</t>
+        </is>
+      </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
@@ -49526,6 +50282,11 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BN153" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
@@ -49847,6 +50608,11 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BN154" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
@@ -50168,6 +50934,11 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BN155" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
@@ -50489,6 +51260,11 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BN156" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
@@ -50810,6 +51586,11 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BN157" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
@@ -51131,6 +51912,11 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BN158" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
@@ -51452,6 +52238,11 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BN159" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
@@ -51773,6 +52564,11 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BN160" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
@@ -52094,6 +52890,11 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BN161" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
@@ -52415,6 +53216,11 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BN162" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
@@ -52736,6 +53542,11 @@
           <t>2error</t>
         </is>
       </c>
+      <c r="BN163" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
@@ -53057,6 +53868,11 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BN164" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
@@ -53378,6 +54194,11 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BN165" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
@@ -53699,6 +54520,11 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BN166" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
@@ -54020,6 +54846,11 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BN167" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
@@ -54339,6 +55170,11 @@
           <t>offline</t>
         </is>
       </c>
+      <c r="BN168" t="inlineStr">
+        <is>
+          <t>offline</t>
+        </is>
+      </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
@@ -54660,6 +55496,11 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BN169" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
@@ -54981,6 +55822,11 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BN170" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
@@ -55302,6 +56148,11 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BN171" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
@@ -55623,6 +56474,11 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BN172" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
@@ -55944,6 +56800,11 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BN173" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
@@ -56265,6 +57126,11 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BN174" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
@@ -56586,6 +57452,11 @@
           <t>1error</t>
         </is>
       </c>
+      <c r="BN175" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
@@ -56907,6 +57778,11 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BN176" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
@@ -57226,6 +58102,11 @@
           <t>offline</t>
         </is>
       </c>
+      <c r="BN177" t="inlineStr">
+        <is>
+          <t>offline</t>
+        </is>
+      </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
@@ -57547,6 +58428,11 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BN178" t="inlineStr">
+        <is>
+          <t>1error</t>
+        </is>
+      </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
@@ -57868,6 +58754,11 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BN179" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
@@ -58189,6 +59080,11 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BN180" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
@@ -58510,6 +59406,11 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BN181" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
@@ -58829,6 +59730,11 @@
           <t>offline</t>
         </is>
       </c>
+      <c r="BN182" t="inlineStr">
+        <is>
+          <t>offline</t>
+        </is>
+      </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
@@ -59150,6 +60056,11 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BN183" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
@@ -59471,6 +60382,11 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BN184" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
@@ -59792,6 +60708,11 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BN185" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
@@ -60113,6 +61034,11 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BN186" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
@@ -60434,6 +61360,11 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BN187" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
@@ -60753,6 +61684,11 @@
           <t>offline</t>
         </is>
       </c>
+      <c r="BN188" t="inlineStr">
+        <is>
+          <t>offline</t>
+        </is>
+      </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
@@ -61074,6 +62010,11 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BN189" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
@@ -61395,6 +62336,11 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BN190" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
@@ -61716,6 +62662,11 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BN191" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
@@ -62037,6 +62988,11 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BN192" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
@@ -62358,6 +63314,11 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BN193" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
@@ -62679,6 +63640,11 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BN194" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
@@ -63000,6 +63966,11 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BN195" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
@@ -63321,6 +64292,11 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BN196" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
@@ -63642,6 +64618,11 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BN197" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
@@ -63963,6 +64944,11 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BN198" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
@@ -64284,6 +65270,11 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BN199" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
@@ -64605,6 +65596,11 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BN200" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
@@ -64926,6 +65922,11 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BN201" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
@@ -65247,6 +66248,11 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BN202" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
@@ -65568,6 +66574,11 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BN203" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
@@ -65889,6 +66900,11 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BN204" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
@@ -66210,6 +67226,11 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BN205" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
@@ -66531,6 +67552,11 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BN206" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
@@ -66544,7 +67570,7 @@
       </c>
       <c r="D207" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E207" t="inlineStr">
@@ -66850,6 +67876,11 @@
       <c r="BM207" t="inlineStr">
         <is>
           <t>1error</t>
+        </is>
+      </c>
+      <c r="BN207" t="inlineStr">
+        <is>
+          <t>online</t>
         </is>
       </c>
     </row>
@@ -67173,6 +68204,11 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BN208" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
@@ -67494,6 +68530,11 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BN209" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
@@ -67815,6 +68856,11 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BN210" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
@@ -68136,6 +69182,11 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BN211" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
@@ -68457,6 +69508,11 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BN212" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
@@ -68778,6 +69834,11 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BN213" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
@@ -69099,6 +70160,11 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BN214" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
@@ -69420,6 +70486,11 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BN215" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
@@ -69741,6 +70812,11 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BN216" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
@@ -70062,6 +71138,11 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BN217" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
@@ -70383,6 +71464,11 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BN218" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
@@ -70704,6 +71790,11 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BN219" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
@@ -71025,6 +72116,11 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BN220" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="221">
       <c r="A221" t="inlineStr">
@@ -71346,6 +72442,11 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BN221" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="222">
       <c r="A222" t="inlineStr">
@@ -71667,6 +72768,11 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BN222" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr">
@@ -71988,6 +73094,11 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BN223" t="inlineStr">
+        <is>
+          <t>1error</t>
+        </is>
+      </c>
     </row>
     <row r="224">
       <c r="A224" t="inlineStr">
@@ -72309,6 +73420,11 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BN224" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="225">
       <c r="A225" t="inlineStr">
@@ -72630,6 +73746,11 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BN225" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="226">
       <c r="A226" t="inlineStr">
@@ -72951,6 +74072,11 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BN226" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="227">
       <c r="A227" t="inlineStr">
@@ -73272,6 +74398,11 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BN227" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="228">
       <c r="A228" t="inlineStr">
@@ -73593,6 +74724,11 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BN228" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="229">
       <c r="A229" t="inlineStr">
@@ -73914,6 +75050,11 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BN229" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="230">
       <c r="A230" t="inlineStr">
@@ -74235,6 +75376,11 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BN230" t="inlineStr">
+        <is>
+          <t>1error</t>
+        </is>
+      </c>
     </row>
     <row r="231">
       <c r="A231" t="inlineStr">
@@ -74556,6 +75702,11 @@
           <t>1error</t>
         </is>
       </c>
+      <c r="BN231" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="232">
       <c r="A232" t="inlineStr">
@@ -74877,6 +76028,11 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BN232" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="233">
       <c r="A233" t="inlineStr">
@@ -75198,6 +76354,11 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BN233" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="234">
       <c r="A234" t="inlineStr">
@@ -75519,6 +76680,11 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BN234" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="235">
       <c r="A235" t="inlineStr">
@@ -75840,6 +77006,11 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BN235" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="236">
       <c r="A236" t="inlineStr">
@@ -76161,6 +77332,11 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BN236" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="237">
       <c r="A237" t="inlineStr">
@@ -76482,6 +77658,11 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BN237" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="238">
       <c r="A238" t="inlineStr">
@@ -76803,6 +77984,11 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BN238" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="239">
       <c r="A239" t="inlineStr">
@@ -77124,6 +78310,11 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BN239" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="240">
       <c r="A240" t="inlineStr">
@@ -77445,6 +78636,11 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BN240" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="241">
       <c r="A241" t="inlineStr">
@@ -77766,6 +78962,11 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BN241" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="242">
       <c r="A242" t="inlineStr">
@@ -78087,6 +79288,11 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BN242" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="243">
       <c r="A243" t="inlineStr">
@@ -78408,6 +79614,11 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BN243" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="244">
       <c r="A244" t="inlineStr">
@@ -78725,6 +79936,11 @@
         </is>
       </c>
       <c r="BM244" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BN244" t="inlineStr">
         <is>
           <t>online</t>
         </is>
@@ -79014,6 +80230,11 @@
         </is>
       </c>
       <c r="BM245" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BN245" t="inlineStr">
         <is>
           <t>online</t>
         </is>
@@ -79275,6 +80496,11 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BN246" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="247">
       <c r="A247" t="inlineStr">
@@ -79528,6 +80754,11 @@
         </is>
       </c>
       <c r="BM247" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BN247" t="inlineStr">
         <is>
           <t>online</t>
         </is>
@@ -79757,6 +80988,11 @@
           <t>1error</t>
         </is>
       </c>
+      <c r="BN248" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="249">
       <c r="A249" t="inlineStr">
@@ -79978,6 +81214,11 @@
         </is>
       </c>
       <c r="BM249" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BN249" t="inlineStr">
         <is>
           <t>online</t>
         </is>
@@ -80203,6 +81444,11 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BN250" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="251">
       <c r="A251" t="inlineStr">
@@ -80424,6 +81670,11 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BN251" t="inlineStr">
+        <is>
+          <t>2error</t>
+        </is>
+      </c>
     </row>
     <row r="252">
       <c r="A252" t="inlineStr">
@@ -80645,6 +81896,11 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BN252" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="253">
       <c r="A253" t="inlineStr">
@@ -80862,6 +82118,11 @@
         </is>
       </c>
       <c r="BM253" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="BN253" t="inlineStr">
         <is>
           <t>online</t>
         </is>
@@ -81007,6 +82268,11 @@
           <t>2error</t>
         </is>
       </c>
+      <c r="BN254" t="inlineStr">
+        <is>
+          <t>2error</t>
+        </is>
+      </c>
     </row>
     <row r="255">
       <c r="A255" t="inlineStr">
@@ -81148,6 +82414,11 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BN255" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="256">
       <c r="A256" t="inlineStr">
@@ -81289,6 +82560,11 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BN256" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="257">
       <c r="A257" t="inlineStr">
@@ -81430,6 +82706,11 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BN257" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="258">
       <c r="A258" t="inlineStr">
@@ -81571,6 +82852,11 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BN258" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
     <row r="259">
       <c r="A259" t="inlineStr">
@@ -81712,6 +82998,11 @@
           <t>online</t>
         </is>
       </c>
+      <c r="BN259" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/UATtracking.xlsx
+++ b/UATtracking.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19209" uniqueCount="344">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19210" uniqueCount="344">
   <si>
     <t>Name</t>
   </si>
@@ -349,7 +349,7 @@
     <t>洛阳龙门服务区（二连浩特方向）</t>
   </si>
   <si>
-    <t>新乡原阳服务区（西侧）</t>
+    <t>G4京港澳高速原阳服务区（广州方向）</t>
   </si>
   <si>
     <t>石家庄东服务区（北京方向）</t>
@@ -424,10 +424,10 @@
     <t>厦门SM广场三期</t>
   </si>
   <si>
-    <t>湖州南浔服务区（北侧）</t>
+    <t>S12申嘉湖高速南浔服务区（上海方向）</t>
   </si>
   <si>
-    <t>湖州南浔服务区（南侧）</t>
+    <t>S12申嘉湖高速南浔服务区（湖州方向）</t>
   </si>
   <si>
     <t>昆明金格时光百货</t>
@@ -484,7 +484,7 @@
     <t>苏州相城天虹广场</t>
   </si>
   <si>
-    <t>新乡原阳服务区（东侧）</t>
+    <t>G4京港澳高速原阳服务区（北京方向）</t>
   </si>
   <si>
     <t>德阳金山服务区（绵阳方向）</t>
@@ -556,10 +556,10 @@
     <t>东莞G4厚街服务区（北行）</t>
   </si>
   <si>
-    <t>杭州西湖服务区（南侧）</t>
+    <t>杭州西湖服务区（萧山方向）</t>
   </si>
   <si>
-    <t>杭州西湖服务区（北侧）</t>
+    <t>杭州西湖服务区（西湖方向）</t>
   </si>
   <si>
     <t>广州中洲中心</t>
@@ -658,7 +658,7 @@
     <t>北京王府中环</t>
   </si>
   <si>
-    <t>汕尾陆河县陆河东收费站出入口</t>
+    <t>汕尾市陆河县陆河东收费站出入口</t>
   </si>
   <si>
     <t>佛山千灯湖环宇荟</t>
@@ -10027,7 +10027,7 @@
         <v>341</v>
       </c>
       <c r="BZ37" t="s">
-        <v>341</v>
+        <v>339</v>
       </c>
     </row>
     <row r="38" spans="1:78">
@@ -25635,7 +25635,7 @@
         <v>342</v>
       </c>
       <c r="BY104" t="s">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="BZ104" t="s">
         <v>340</v>
@@ -25868,7 +25868,7 @@
         <v>339</v>
       </c>
       <c r="BY105" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="BZ105" t="s">
         <v>340</v>
@@ -42880,7 +42880,7 @@
         <v>341</v>
       </c>
       <c r="BZ178" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
     </row>
     <row r="179" spans="1:78">
@@ -44045,7 +44045,7 @@
         <v>341</v>
       </c>
       <c r="BZ183" t="s">
-        <v>339</v>
+        <v>341</v>
       </c>
     </row>
     <row r="184" spans="1:78">
@@ -44987,8 +44987,8 @@
       <c r="C188">
         <v>2</v>
       </c>
-      <c r="D188">
-        <v>1</v>
+      <c r="D188" t="s">
+        <v>336</v>
       </c>
       <c r="E188" t="s">
         <v>339</v>
@@ -45210,7 +45210,7 @@
         <v>340</v>
       </c>
       <c r="BZ188" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
     </row>
     <row r="189" spans="1:78">
@@ -49870,7 +49870,7 @@
         <v>339</v>
       </c>
       <c r="BZ208" t="s">
-        <v>339</v>
+        <v>341</v>
       </c>
     </row>
     <row r="209" spans="1:78">
@@ -55695,7 +55695,7 @@
         <v>341</v>
       </c>
       <c r="BZ233" t="s">
-        <v>341</v>
+        <v>339</v>
       </c>
     </row>
     <row r="234" spans="1:78">
